--- a/research/traditional_assets/database/data/germany/germany_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03623</v>
+        <v>0.04994999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.0253</v>
+        <v>0.04326000000000001</v>
       </c>
       <c r="F2">
-        <v>0.0795</v>
+        <v>0.2035</v>
       </c>
       <c r="G2">
-        <v>0.07036326484877148</v>
+        <v>0.07868560384419802</v>
       </c>
       <c r="H2">
-        <v>0.06478740758226502</v>
+        <v>0.06533477628752149</v>
       </c>
       <c r="I2">
-        <v>0.05833683273769434</v>
+        <v>0.06277435687290096</v>
       </c>
       <c r="J2">
-        <v>0.04799554621763265</v>
+        <v>0.05456300391260824</v>
       </c>
       <c r="K2">
-        <v>4549.3</v>
+        <v>5612.107</v>
       </c>
       <c r="L2">
-        <v>0.1264897150818681</v>
+        <v>0.1733802447914317</v>
       </c>
       <c r="M2">
-        <v>787.254</v>
+        <v>1262.6452</v>
       </c>
       <c r="N2">
-        <v>0.01205271230195607</v>
+        <v>0.02112252163032059</v>
       </c>
       <c r="O2">
-        <v>0.1730494801398017</v>
+        <v>0.2249859455637606</v>
       </c>
       <c r="P2">
-        <v>787.254</v>
+        <v>1262.6442</v>
       </c>
       <c r="Q2">
-        <v>0.01205271230195607</v>
+        <v>0.02112250490153436</v>
       </c>
       <c r="R2">
-        <v>0.1730494801398017</v>
+        <v>0.2249857673775643</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>7.919881214453593e-07</v>
       </c>
       <c r="U2">
-        <v>243406.851</v>
+        <v>190238.85</v>
       </c>
       <c r="V2">
-        <v>3.726513612414912</v>
+        <v>3.182465053565574</v>
       </c>
       <c r="W2">
-        <v>0.06122183483374096</v>
+        <v>0.06204919144803849</v>
       </c>
       <c r="X2">
-        <v>0.02746967025716149</v>
+        <v>0.05141193991815046</v>
       </c>
       <c r="Y2">
-        <v>0.03375216457657947</v>
+        <v>0.01063725152988804</v>
       </c>
       <c r="Z2">
-        <v>0.06040226965129185</v>
+        <v>0.06595868448746389</v>
       </c>
       <c r="AA2">
-        <v>0.0003630447795600678</v>
+        <v>0.0004082514267073862</v>
       </c>
       <c r="AB2">
-        <v>0.02306796671994329</v>
+        <v>0.04691063072238714</v>
       </c>
       <c r="AC2">
-        <v>-0.02471203676022268</v>
+        <v>-0.04263502182954543</v>
       </c>
       <c r="AD2">
-        <v>642513.4700000001</v>
+        <v>657594.21</v>
       </c>
       <c r="AE2">
-        <v>13.70445613807446</v>
+        <v>15.84326369790463</v>
       </c>
       <c r="AF2">
-        <v>642527.1744561382</v>
+        <v>657610.0532636979</v>
       </c>
       <c r="AG2">
-        <v>399120.3234561381</v>
+        <v>467371.2032636979</v>
       </c>
       <c r="AH2">
-        <v>0.9077232972501353</v>
+        <v>0.9166737355200442</v>
       </c>
       <c r="AI2">
-        <v>0.8719903025349008</v>
+        <v>0.8836805409015575</v>
       </c>
       <c r="AJ2">
-        <v>0.8593620815313825</v>
+        <v>0.8866027106789939</v>
       </c>
       <c r="AK2">
-        <v>0.8088455282809784</v>
+        <v>0.8437325941402637</v>
       </c>
       <c r="AL2">
-        <v>99.223</v>
+        <v>105.715</v>
       </c>
       <c r="AM2">
-        <v>-27.73100000000001</v>
+        <v>8.138999999999996</v>
       </c>
       <c r="AN2">
-        <v>277.0786261500678</v>
+        <v>297.1047886430513</v>
       </c>
       <c r="AO2">
-        <v>21.11667657700332</v>
+        <v>19.1714042472686</v>
       </c>
       <c r="AP2">
-        <v>172.1173423676198</v>
+        <v>211.1609567905252</v>
       </c>
       <c r="AQ2">
-        <v>-75.5565973098698</v>
+        <v>249.0115493303847</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hypoport SE (XTRA:HYQ)</t>
+          <t>aifinyo AG (XTRA:EBE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,32 +724,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.234</v>
-      </c>
-      <c r="E3">
-        <v>0.152</v>
-      </c>
-      <c r="F3">
-        <v>0.373</v>
-      </c>
       <c r="G3">
-        <v>0.1603868627846061</v>
+        <v>0.04497153700189753</v>
       </c>
       <c r="H3">
-        <v>0.1007455168245013</v>
+        <v>0.04497153700189753</v>
       </c>
       <c r="I3">
-        <v>0.1059842836993754</v>
+        <v>0.02846299810246679</v>
       </c>
       <c r="J3">
-        <v>0.0891871835220715</v>
+        <v>0.02651248808021653</v>
       </c>
       <c r="K3">
-        <v>40.4</v>
+        <v>0.734</v>
       </c>
       <c r="L3">
-        <v>0.08140237759419705</v>
+        <v>0.01392789373814042</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -773,73 +764,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.01508874927985515</v>
-      </c>
-      <c r="W3">
-        <v>0.1632323232323232</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.02329403695934897</v>
-      </c>
-      <c r="Y3">
-        <v>0.1399382862729743</v>
-      </c>
-      <c r="Z3">
-        <v>3.181410256410255</v>
-      </c>
-      <c r="AA3">
-        <v>0.283741020397462</v>
+        <v>0.04813485421146283</v>
       </c>
       <c r="AB3">
-        <v>0.02306796671994329</v>
-      </c>
-      <c r="AC3">
-        <v>0.2606730536775187</v>
+        <v>0.04813485421146283</v>
       </c>
       <c r="AD3">
-        <v>235.9</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>235.9</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>180.9</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.06078330327235248</v>
-      </c>
-      <c r="AI3">
-        <v>0.4505347593582887</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.04728175640355463</v>
-      </c>
-      <c r="AK3">
-        <v>0.3860435339308579</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>4.01</v>
+        <v>0.792</v>
       </c>
       <c r="AM3">
-        <v>3.764</v>
+        <v>0.7310000000000001</v>
       </c>
       <c r="AN3">
-        <v>3.892739273927393</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>13.11720698254364</v>
+        <v>1.893939393939394</v>
       </c>
       <c r="AP3">
-        <v>2.985148514851485</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>13.97449521785335</v>
+        <v>2.051983584131327</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DF Deutsche Forfait AG (XTRA:DFTK)</t>
+          <t>Stock3 AG (MUN:BOG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,22 +829,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.4433962264150944</v>
+        <v>0.1385185185185185</v>
       </c>
       <c r="H4">
-        <v>0.4433962264150944</v>
+        <v>0.1385185185185185</v>
       </c>
       <c r="I4">
-        <v>0.489622641509434</v>
+        <v>0.1428865420639299</v>
       </c>
       <c r="J4">
-        <v>0.489622641509434</v>
+        <v>0.09799094106316103</v>
       </c>
       <c r="K4">
-        <v>8.529999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="L4">
-        <v>0.8047169811320755</v>
+        <v>0.08962962962962963</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -898,73 +868,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8.43</v>
+        <v>5.73</v>
       </c>
       <c r="V4">
-        <v>0.386697247706422</v>
-      </c>
-      <c r="W4">
-        <v>0.7754545454545454</v>
+        <v>0.203914590747331</v>
       </c>
       <c r="X4">
-        <v>0.02746967025716149</v>
-      </c>
-      <c r="Y4">
-        <v>0.7479848751973839</v>
+        <v>0.04853718672279859</v>
       </c>
       <c r="Z4">
-        <v>0.5273631840796019</v>
+        <v>7.802753734357315</v>
       </c>
       <c r="AA4">
-        <v>0.2582089552238806</v>
+        <v>0.7645991813137673</v>
       </c>
       <c r="AB4">
-        <v>0.02389910559689818</v>
+        <v>0.04810930761200346</v>
       </c>
       <c r="AC4">
-        <v>0.2343098496269824</v>
+        <v>0.7164898737017638</v>
       </c>
       <c r="AD4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.730158410684731</v>
       </c>
       <c r="AF4">
-        <v>18</v>
+        <v>1.730158410684731</v>
       </c>
       <c r="AG4">
-        <v>9.57</v>
+        <v>-3.999841589315269</v>
       </c>
       <c r="AH4">
-        <v>0.4522613065326633</v>
+        <v>0.05800030917921686</v>
       </c>
       <c r="AI4">
-        <v>0.4724409448818898</v>
+        <v>0.2617423521784416</v>
       </c>
       <c r="AJ4">
-        <v>0.3050685368186165</v>
+        <v>-0.1659674397634645</v>
       </c>
       <c r="AK4">
-        <v>0.3225480283114256</v>
+        <v>-4.544456475969526</v>
       </c>
       <c r="AL4">
-        <v>0.096</v>
+        <v>0.003</v>
       </c>
       <c r="AM4">
-        <v>0.096</v>
+        <v>0.002</v>
       </c>
       <c r="AN4">
-        <v>3.409090909090909</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>54.0625</v>
+        <v>586.6666666666666</v>
       </c>
       <c r="AP4">
-        <v>1.8125</v>
+        <v>-1.677082427385857</v>
       </c>
       <c r="AQ4">
-        <v>54.0625</v>
+        <v>880</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deutsche Börse AG (XTRA:DB1)</t>
+          <t>DF Deutsche Forfait AG (XTRA:DFTK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -983,125 +947,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.08890000000000001</v>
-      </c>
-      <c r="E5">
-        <v>-0.00805</v>
-      </c>
-      <c r="F5">
-        <v>0.0795</v>
-      </c>
       <c r="G5">
-        <v>0.5041902324237295</v>
+        <v>0.5385964912280702</v>
       </c>
       <c r="H5">
-        <v>0.4699459191677331</v>
+        <v>0.5385964912280702</v>
       </c>
       <c r="I5">
-        <v>0.4196424885439458</v>
+        <v>0.5280701754385965</v>
       </c>
       <c r="J5">
-        <v>0.3094581424371652</v>
+        <v>0.5280701754385965</v>
       </c>
       <c r="K5">
-        <v>1341.4</v>
+        <v>7.5</v>
       </c>
       <c r="L5">
-        <v>0.2768856045906783</v>
+        <v>0.6578947368421052</v>
       </c>
       <c r="M5">
-        <v>638.58</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.02089177225750096</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.4760548680483077</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>638.58</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.02089177225750096</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.4760548680483077</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>0.5662650602409639</v>
       </c>
       <c r="W5">
-        <v>0.1900699974494857</v>
+        <v>0.3731343283582089</v>
       </c>
       <c r="X5">
-        <v>0.02393497079361919</v>
+        <v>0.05262233232034677</v>
       </c>
       <c r="Y5">
-        <v>0.1661350266558665</v>
+        <v>0.3205119960378622</v>
       </c>
       <c r="Z5">
-        <v>0.421339177777198</v>
+        <v>0.3842264914054601</v>
       </c>
       <c r="AA5">
-        <v>0.1303868392909343</v>
+        <v>0.2028985507246377</v>
       </c>
       <c r="AB5">
-        <v>0.02276847833840035</v>
+        <v>0.04687252558991987</v>
       </c>
       <c r="AC5">
-        <v>0.1076183609525339</v>
+        <v>0.1560260251347178</v>
       </c>
       <c r="AD5">
-        <v>5548.4</v>
+        <v>17.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>5548.4</v>
+        <v>17.1</v>
       </c>
       <c r="AG5">
-        <v>5548.4</v>
+        <v>3.000000000000002</v>
       </c>
       <c r="AH5">
-        <v>0.1536335820792203</v>
+        <v>0.4071428571428572</v>
       </c>
       <c r="AI5">
-        <v>0.3971738834763811</v>
+        <v>0.4042553191489363</v>
       </c>
       <c r="AJ5">
-        <v>0.1536335820792203</v>
+        <v>0.1075268817204302</v>
       </c>
       <c r="AK5">
-        <v>0.3971738834763811</v>
+        <v>0.1063829787234043</v>
       </c>
       <c r="AL5">
-        <v>88</v>
+        <v>0.222</v>
       </c>
       <c r="AM5">
-        <v>-34.90000000000001</v>
+        <v>-0.415</v>
       </c>
       <c r="AN5">
-        <v>2.471447661469933</v>
+        <v>2.798690671031097</v>
       </c>
       <c r="AO5">
-        <v>23.10227272727273</v>
+        <v>27.11711711711711</v>
       </c>
       <c r="AP5">
-        <v>2.471447661469933</v>
+        <v>0.4909983633387892</v>
       </c>
       <c r="AQ5">
-        <v>-58.25214899713466</v>
+        <v>-14.50602409638554</v>
       </c>
     </row>
     <row r="6">
@@ -1112,7 +1064,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fast Finance24 Holding AG (XTRA:FF24)</t>
+          <t>Hypoport SE (XTRA:HYQ)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1120,8 +1072,32 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.212</v>
+      </c>
+      <c r="E6">
+        <v>0.08380000000000001</v>
+      </c>
+      <c r="F6">
+        <v>0.276</v>
+      </c>
+      <c r="G6">
+        <v>0.237160751565762</v>
+      </c>
+      <c r="H6">
+        <v>0.1688935281837161</v>
+      </c>
+      <c r="I6">
+        <v>0.08225469728601252</v>
+      </c>
+      <c r="J6">
+        <v>0.05716004387672056</v>
+      </c>
       <c r="K6">
-        <v>2.07</v>
+        <v>28.9</v>
+      </c>
+      <c r="L6">
+        <v>0.06033402922755741</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1145,64 +1121,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.142</v>
+        <v>33.4</v>
       </c>
       <c r="V6">
-        <v>0.0195054945054945</v>
+        <v>0.05090687395214144</v>
       </c>
       <c r="W6">
-        <v>0.04736842105263157</v>
+        <v>0.1009783368273934</v>
       </c>
       <c r="X6">
-        <v>0.02293891894203839</v>
+        <v>0.04991958841705024</v>
       </c>
       <c r="Y6">
-        <v>0.02442950211059319</v>
+        <v>0.05105874841034319</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.283126787416587</v>
       </c>
       <c r="AA6">
-        <v>0.05153123463449403</v>
+        <v>0.1305036273448482</v>
       </c>
       <c r="AB6">
-        <v>0.02293891894203839</v>
+        <v>0.04746970185613153</v>
       </c>
       <c r="AC6">
-        <v>0.02859231569245564</v>
+        <v>0.08303392548871666</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>179.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>179.2</v>
       </c>
       <c r="AG6">
-        <v>-0.142</v>
+        <v>145.8</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.2145337004668981</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.396547908829387</v>
       </c>
       <c r="AJ6">
-        <v>-0.01989352759876716</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AK6">
-        <v>-0.002924337905185551</v>
+        <v>0.3483870967741935</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AM6">
-        <v>-0.004</v>
+        <v>3.034</v>
+      </c>
+      <c r="AN6">
+        <v>2.552706552706552</v>
+      </c>
+      <c r="AO6">
+        <v>12.23602484472049</v>
+      </c>
+      <c r="AP6">
+        <v>2.076923076923077</v>
       </c>
       <c r="AQ6">
-        <v>-640</v>
+        <v>12.98615688859591</v>
       </c>
     </row>
     <row r="7">
@@ -1213,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ALBIS Leasing AG (XTRA:ALG)</t>
+          <t>Deutsche Börse AG (XTRA:DB1)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1222,46 +1207,49 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0638</v>
+        <v>0.113</v>
       </c>
       <c r="E7">
-        <v>-0.212</v>
+        <v>0.113</v>
+      </c>
+      <c r="F7">
+        <v>0.124</v>
       </c>
       <c r="G7">
-        <v>0.2186046511627907</v>
+        <v>0.4946183652131128</v>
       </c>
       <c r="H7">
-        <v>0.2186046511627907</v>
+        <v>0.4139861000061504</v>
       </c>
       <c r="I7">
-        <v>0.2395348837209302</v>
+        <v>0.4053139799495664</v>
       </c>
       <c r="J7">
-        <v>0.1919700996677741</v>
+        <v>0.2999150328600677</v>
       </c>
       <c r="K7">
-        <v>1.68</v>
+        <v>1388.9</v>
       </c>
       <c r="L7">
-        <v>0.05581395348837209</v>
+        <v>0.2847448592574369</v>
       </c>
       <c r="M7">
-        <v>0.9964</v>
+        <v>576.504</v>
       </c>
       <c r="N7">
-        <v>0.01364931506849315</v>
+        <v>0.01820151925590559</v>
       </c>
       <c r="O7">
-        <v>0.5930952380952381</v>
+        <v>0.4150795593635251</v>
       </c>
       <c r="P7">
-        <v>0.9964</v>
+        <v>576.504</v>
       </c>
       <c r="Q7">
-        <v>0.01364931506849315</v>
+        <v>0.01820151925590559</v>
       </c>
       <c r="R7">
-        <v>0.5930952380952381</v>
+        <v>0.4150795593635251</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1270,73 +1258,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>0.1424657534246575</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>0.08484848484848484</v>
+        <v>0.1768668500407498</v>
       </c>
       <c r="X7">
-        <v>0.03968628604067272</v>
+        <v>0.0491959455046638</v>
       </c>
       <c r="Y7">
-        <v>0.04516219880781212</v>
+        <v>0.127670904536086</v>
       </c>
       <c r="Z7">
-        <v>0.1386713351147148</v>
+        <v>0.3639748679222756</v>
       </c>
       <c r="AA7">
-        <v>0.0266207500230351</v>
+        <v>0.1091615344731481</v>
       </c>
       <c r="AB7">
-        <v>0.02210330837396964</v>
+        <v>0.04694873585485441</v>
       </c>
       <c r="AC7">
-        <v>0.004517441649065462</v>
+        <v>0.06221279861829367</v>
       </c>
       <c r="AD7">
-        <v>222.8</v>
+        <v>5143.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>222.8</v>
+        <v>5143.3</v>
       </c>
       <c r="AG7">
-        <v>212.4</v>
+        <v>5143.3</v>
       </c>
       <c r="AH7">
-        <v>0.7532116294793779</v>
+        <v>0.1397001904027248</v>
       </c>
       <c r="AI7">
-        <v>0.8761305544632324</v>
+        <v>0.3682571277189868</v>
       </c>
       <c r="AJ7">
-        <v>0.7442186405045551</v>
+        <v>0.1397001904027248</v>
       </c>
       <c r="AK7">
-        <v>0.8708487084870848</v>
+        <v>0.3682571277189868</v>
       </c>
       <c r="AL7">
-        <v>6.99</v>
+        <v>94</v>
       </c>
       <c r="AM7">
-        <v>6.437</v>
+        <v>17.5</v>
       </c>
       <c r="AN7">
-        <v>30.56241426611797</v>
+        <v>2.422314322045872</v>
       </c>
       <c r="AO7">
-        <v>1.031473533619456</v>
+        <v>21.03191489361702</v>
       </c>
       <c r="AP7">
-        <v>29.1358024691358</v>
+        <v>2.422314322045872</v>
       </c>
       <c r="AQ7">
-        <v>1.120086997048314</v>
+        <v>112.9714285714286</v>
       </c>
     </row>
     <row r="8">
@@ -1347,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Grenke AG (XTRA:GLJ)</t>
+          <t>ALBIS Leasing AG (XTRA:ALG)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1356,49 +1344,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.102</v>
+        <v>0.0263</v>
       </c>
       <c r="E8">
-        <v>-0.0253</v>
-      </c>
-      <c r="F8">
-        <v>0.045</v>
+        <v>-0.805</v>
       </c>
       <c r="G8">
-        <v>0.008432323908315208</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="I8">
-        <v>0.004800248908122984</v>
+        <v>0.2181481481481481</v>
       </c>
       <c r="J8">
-        <v>0.003555739931942951</v>
+        <v>0.2181481481481481</v>
       </c>
       <c r="K8">
-        <v>99</v>
+        <v>0.001</v>
       </c>
       <c r="L8">
-        <v>0.1656349339133344</v>
+        <v>3.703703703703704e-05</v>
       </c>
       <c r="M8">
-        <v>29.5</v>
+        <v>0.886</v>
       </c>
       <c r="N8">
-        <v>0.01828210213187903</v>
+        <v>0.01881104033970276</v>
       </c>
       <c r="O8">
-        <v>0.297979797979798</v>
+        <v>886</v>
       </c>
       <c r="P8">
-        <v>29.5</v>
+        <v>0.886</v>
       </c>
       <c r="Q8">
-        <v>0.01828210213187903</v>
+        <v>0.01881104033970276</v>
       </c>
       <c r="R8">
-        <v>0.297979797979798</v>
+        <v>886</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1407,70 +1392,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1180.2</v>
+        <v>15.2</v>
       </c>
       <c r="V8">
-        <v>0.7314080317302926</v>
+        <v>0.3227176220806794</v>
       </c>
       <c r="W8">
-        <v>0.06690545380820437</v>
+        <v>3.174603174603174e-05</v>
       </c>
       <c r="X8">
-        <v>0.03792513409565879</v>
+        <v>0.07812926687309307</v>
       </c>
       <c r="Y8">
-        <v>0.02898031971254558</v>
+        <v>-0.07809752084134704</v>
       </c>
       <c r="Z8">
-        <v>0.102101049713636</v>
+        <v>0.1184730144800351</v>
       </c>
       <c r="AA8">
-        <v>0.0003630447795600678</v>
+        <v>0.0258446687143484</v>
       </c>
       <c r="AB8">
-        <v>0.02507508153978275</v>
+        <v>0.04777318826328403</v>
       </c>
       <c r="AC8">
-        <v>-0.02471203676022268</v>
+        <v>-0.02192851954893563</v>
       </c>
       <c r="AD8">
-        <v>4393.2</v>
+        <v>216.2</v>
       </c>
       <c r="AE8">
-        <v>13.70445613807446</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>4406.904456138074</v>
+        <v>216.2</v>
       </c>
       <c r="AG8">
-        <v>3226.704456138074</v>
+        <v>201</v>
       </c>
       <c r="AH8">
-        <v>0.7319825918648911</v>
+        <v>0.8211165970375996</v>
       </c>
       <c r="AI8">
-        <v>0.7560692928078151</v>
+        <v>0.8871563397620025</v>
       </c>
       <c r="AJ8">
-        <v>0.6666325404482015</v>
+        <v>0.8101571946795647</v>
       </c>
       <c r="AK8">
-        <v>0.6941381871490738</v>
+        <v>0.8796498905908097</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="AM8">
-        <v>-3.23</v>
+        <v>6.987</v>
       </c>
       <c r="AN8">
-        <v>783.1016042780748</v>
+        <v>35.44262295081968</v>
+      </c>
+      <c r="AO8">
+        <v>0.8157894736842105</v>
       </c>
       <c r="AP8">
-        <v>575.1701347839704</v>
+        <v>32.95081967213115</v>
       </c>
       <c r="AQ8">
-        <v>-0</v>
+        <v>0.842994131959353</v>
       </c>
     </row>
     <row r="9">
@@ -1490,7 +1478,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.09050000000000001</v>
+        <v>-0.0244</v>
+      </c>
+      <c r="E9">
+        <v>-0.104</v>
+      </c>
+      <c r="F9">
+        <v>0.5579999999999999</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1505,28 +1499,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>-40.6</v>
+        <v>110.8</v>
       </c>
       <c r="L9">
-        <v>-0.062557781201849</v>
+        <v>0.1518640350877193</v>
       </c>
       <c r="M9">
-        <v>27.7936</v>
+        <v>94.04300000000001</v>
       </c>
       <c r="N9">
-        <v>0.01425897804227375</v>
+        <v>0.04446687786656579</v>
       </c>
       <c r="O9">
-        <v>-0.6845714285714286</v>
+        <v>0.8487635379061372</v>
       </c>
       <c r="P9">
-        <v>27.7936</v>
+        <v>94.04300000000001</v>
       </c>
       <c r="Q9">
-        <v>0.01425897804227375</v>
+        <v>0.04446687786656579</v>
       </c>
       <c r="R9">
-        <v>-0.6845714285714286</v>
+        <v>0.8487635379061372</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1535,55 +1529,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>6252.9</v>
+        <v>8161.4</v>
       </c>
       <c r="V9">
-        <v>3.207931459060127</v>
+        <v>3.859000425552035</v>
       </c>
       <c r="W9">
-        <v>-0.01216989898384341</v>
+        <v>0.03215508735271925</v>
       </c>
       <c r="X9">
-        <v>0.1270084904659931</v>
+        <v>0.1590524667774009</v>
       </c>
       <c r="Y9">
-        <v>-0.1391783894498365</v>
+        <v>-0.1268973794246817</v>
       </c>
       <c r="Z9">
-        <v>0.0190234436829856</v>
+        <v>0.0213577511131147</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.02495566214473383</v>
+        <v>0.04011676125404851</v>
       </c>
       <c r="AC9">
-        <v>-0.02495566214473383</v>
+        <v>-0.04011676125404851</v>
       </c>
       <c r="AD9">
-        <v>36968</v>
+        <v>35899.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>36968</v>
+        <v>35899.2</v>
       </c>
       <c r="AG9">
-        <v>30715.1</v>
+        <v>27737.8</v>
       </c>
       <c r="AH9">
-        <v>0.9499141767650294</v>
+        <v>0.9443653802141836</v>
       </c>
       <c r="AI9">
-        <v>0.9130358540940648</v>
+        <v>0.9180958421351447</v>
       </c>
       <c r="AJ9">
-        <v>0.9403262889454236</v>
+        <v>0.9291554867733907</v>
       </c>
       <c r="AK9">
-        <v>0.8971527213884719</v>
+        <v>0.8964913187935515</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1609,10 +1603,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0247</v>
+        <v>-0.01</v>
       </c>
       <c r="F10">
-        <v>0.023</v>
+        <v>0.276</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1627,82 +1621,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>2867.4</v>
+        <v>3784.1</v>
       </c>
       <c r="L10">
-        <v>0.09979396656132976</v>
+        <v>0.1502909228111285</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>399.2912</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.01732125055851745</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.1055181416981581</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>399.2912</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.01732125055851745</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.1055181416981581</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>228201.2</v>
+        <v>178515.4</v>
       </c>
       <c r="V10">
-        <v>8.858054498874312</v>
+        <v>7.743997293088266</v>
       </c>
       <c r="W10">
-        <v>0.04032559748657642</v>
+        <v>0.05064326217500639</v>
       </c>
       <c r="X10">
-        <v>0.1411809598747453</v>
+        <v>0.2120147858895722</v>
       </c>
       <c r="Y10">
-        <v>-0.1008553623881688</v>
+        <v>-0.1613715237145658</v>
       </c>
       <c r="Z10">
-        <v>0.05670570431771867</v>
+        <v>0.06268722638059539</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.02496784233512427</v>
+        <v>0.04515328240504234</v>
       </c>
       <c r="AC10">
-        <v>-0.02496784233512427</v>
+        <v>-0.04515328240504234</v>
       </c>
       <c r="AD10">
-        <v>555133.3</v>
+        <v>578136.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>555133.3</v>
+        <v>578136.9</v>
       </c>
       <c r="AG10">
-        <v>326932.1</v>
+        <v>399621.5</v>
       </c>
       <c r="AH10">
-        <v>0.955651216320738</v>
+        <v>0.9616558187192381</v>
       </c>
       <c r="AI10">
-        <v>0.8787261309022366</v>
+        <v>0.8926396437945124</v>
       </c>
       <c r="AJ10">
-        <v>0.9269565325873044</v>
+        <v>0.9454612258726356</v>
       </c>
       <c r="AK10">
-        <v>0.8101470809071369</v>
+        <v>0.8517886492693151</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1719,7 +1716,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deutsche Pfandbriefbank AG (XTRA:PBB)</t>
+          <t>Linus Digital Finance AG (DB:LDF)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1727,113 +1724,92 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.005739999999999999</v>
-      </c>
-      <c r="E11">
-        <v>-0.0596</v>
-      </c>
-      <c r="F11">
-        <v>0.356</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
       <c r="K11">
-        <v>235.3</v>
-      </c>
-      <c r="L11">
-        <v>0.4092885719255523</v>
+        <v>-14.3</v>
       </c>
       <c r="M11">
-        <v>90.384</v>
+        <v>0.001</v>
       </c>
       <c r="N11">
-        <v>0.05616005964955884</v>
+        <v>5.025125628140704e-05</v>
       </c>
       <c r="O11">
-        <v>0.3841223969400765</v>
+        <v>-6.993006993006993e-05</v>
       </c>
       <c r="P11">
-        <v>90.384</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.05616005964955884</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.3841223969400765</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>7693.6</v>
+        <v>7.77</v>
       </c>
       <c r="V11">
-        <v>4.780415061513607</v>
+        <v>0.3904522613065327</v>
       </c>
       <c r="W11">
-        <v>0.06122183483374096</v>
+        <v>-0.6244541484716158</v>
       </c>
       <c r="X11">
-        <v>0.1592833100487718</v>
+        <v>0.1040876889020802</v>
       </c>
       <c r="Y11">
-        <v>-0.09806147521503081</v>
+        <v>-0.728541837373696</v>
       </c>
       <c r="Z11">
-        <v>0.01561774158057304</v>
+        <v>0</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.02574433787332613</v>
+        <v>0.04535861801971307</v>
       </c>
       <c r="AC11">
-        <v>-0.02574433787332613</v>
+        <v>-0.04535861801971307</v>
       </c>
       <c r="AD11">
-        <v>39989.6</v>
+        <v>170.4</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>39989.6</v>
+        <v>170.4</v>
       </c>
       <c r="AG11">
-        <v>32296</v>
+        <v>162.63</v>
       </c>
       <c r="AH11">
-        <v>0.9613115699896632</v>
+        <v>0.8954282711508145</v>
       </c>
       <c r="AI11">
-        <v>0.9103690685413006</v>
+        <v>0.8645357686453577</v>
       </c>
       <c r="AJ11">
-        <v>0.9525326349195113</v>
+        <v>0.8909768257272777</v>
       </c>
       <c r="AK11">
-        <v>0.8913372266319288</v>
+        <v>0.858976390429409</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>-18.1</v>
+      </c>
+      <c r="AQ11">
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -1844,7 +1820,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FORIS AG (XTRA:FRS)</t>
+          <t>Grenke AG (XTRA:GLJ)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1853,115 +1829,121 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.008659999999999999</v>
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="E12">
+        <v>0.00272</v>
+      </c>
+      <c r="F12">
+        <v>0.131</v>
       </c>
       <c r="G12">
-        <v>-0.02087962962962963</v>
+        <v>0.01276993355481728</v>
       </c>
       <c r="H12">
-        <v>-0.02087962962962963</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>-0.0537037037037037</v>
+        <v>0.01043663249280385</v>
       </c>
       <c r="J12">
-        <v>-0.0537037037037037</v>
+        <v>0.007854293909782633</v>
       </c>
       <c r="K12">
-        <v>-2.17</v>
+        <v>106</v>
       </c>
       <c r="L12">
-        <v>-0.1004629629629629</v>
+        <v>0.2200996677740864</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>35.9</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.03689998972145133</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>0.3386792452830188</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>35.9</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.03689998972145133</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>0.3386792452830188</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>4.07</v>
+        <v>450.7</v>
       </c>
       <c r="V12">
-        <v>0.2970802919708029</v>
+        <v>0.4632541885085826</v>
       </c>
       <c r="W12">
-        <v>-0.1142105263157895</v>
+        <v>0.07274723766385287</v>
       </c>
       <c r="X12">
-        <v>0.02388817197304873</v>
+        <v>0.07296757186062892</v>
       </c>
       <c r="Y12">
-        <v>-0.1380986982888382</v>
+        <v>-0.0002203341967760564</v>
       </c>
       <c r="Z12">
-        <v>1.782178217821782</v>
+        <v>0.1039562388157905</v>
       </c>
       <c r="AA12">
-        <v>-0.09570957095709569</v>
+        <v>0.0008165028534147723</v>
       </c>
       <c r="AB12">
-        <v>0.02277530535116679</v>
+        <v>0.04673321942091445</v>
       </c>
       <c r="AC12">
-        <v>-0.1184848763082625</v>
+        <v>-0.04591671656749968</v>
       </c>
       <c r="AD12">
-        <v>2.37</v>
+        <v>3684</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>13.31858895732833</v>
       </c>
       <c r="AF12">
-        <v>2.37</v>
+        <v>3697.318588957328</v>
       </c>
       <c r="AG12">
-        <v>-1.7</v>
+        <v>3246.618588957328</v>
       </c>
       <c r="AH12">
-        <v>0.1474797759800871</v>
+        <v>0.7916799863928404</v>
       </c>
       <c r="AI12">
-        <v>0.1175012394645513</v>
+        <v>0.7415223932189894</v>
       </c>
       <c r="AJ12">
-        <v>-0.1416666666666667</v>
+        <v>0.7694286730846207</v>
       </c>
       <c r="AK12">
-        <v>-0.1055900621118012</v>
+        <v>0.71583659264926</v>
       </c>
       <c r="AL12">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>0.031</v>
+        <v>-1.84</v>
       </c>
       <c r="AN12">
-        <v>-2.59016393442623</v>
-      </c>
-      <c r="AO12">
-        <v>-37.41935483870967</v>
+        <v>479.0637191157347</v>
       </c>
       <c r="AP12">
-        <v>1.85792349726776</v>
+        <v>422.1870726862585</v>
       </c>
       <c r="AQ12">
-        <v>-37.41935483870967</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -1972,121 +1954,487 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Deutsche Pfandbriefbank AG (XTRA:PBB)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.091</v>
+      </c>
+      <c r="E13">
+        <v>0.0866</v>
+      </c>
+      <c r="F13">
+        <v>0.0177</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>202</v>
+      </c>
+      <c r="L13">
+        <v>0.417873396772859</v>
+      </c>
+      <c r="M13">
+        <v>156.02</v>
+      </c>
+      <c r="N13">
+        <v>0.1493300153139357</v>
+      </c>
+      <c r="O13">
+        <v>0.7723762376237623</v>
+      </c>
+      <c r="P13">
+        <v>156.02</v>
+      </c>
+      <c r="Q13">
+        <v>0.1493300153139357</v>
+      </c>
+      <c r="R13">
+        <v>0.7723762376237623</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>3025.1</v>
+      </c>
+      <c r="V13">
+        <v>2.895386676875957</v>
+      </c>
+      <c r="W13">
+        <v>0.05135114523222412</v>
+      </c>
+      <c r="X13">
+        <v>0.261659816255382</v>
+      </c>
+      <c r="Y13">
+        <v>-0.2103086710231579</v>
+      </c>
+      <c r="Z13">
+        <v>0.01334264429459808</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.04641696951678301</v>
+      </c>
+      <c r="AC13">
+        <v>-0.04641696951678301</v>
+      </c>
+      <c r="AD13">
+        <v>34141</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>34141</v>
+      </c>
+      <c r="AG13">
+        <v>31115.9</v>
+      </c>
+      <c r="AH13">
+        <v>0.9703062030705568</v>
+      </c>
+      <c r="AI13">
+        <v>0.9111288432952329</v>
+      </c>
+      <c r="AJ13">
+        <v>0.9675131449253281</v>
+      </c>
+      <c r="AK13">
+        <v>0.9033240434302967</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FORIS AG (XTRA:FRS)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.0337</v>
+      </c>
+      <c r="G14">
+        <v>-0.05958333333333333</v>
+      </c>
+      <c r="H14">
+        <v>-0.05958333333333333</v>
+      </c>
+      <c r="I14">
+        <v>-0.03979166666666666</v>
+      </c>
+      <c r="J14">
+        <v>-0.03979166666666666</v>
+      </c>
+      <c r="K14">
+        <v>-1.34</v>
+      </c>
+      <c r="L14">
+        <v>-0.05583333333333334</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>3.26</v>
+      </c>
+      <c r="V14">
+        <v>0.2527131782945736</v>
+      </c>
+      <c r="W14">
+        <v>-0.07528089887640449</v>
+      </c>
+      <c r="X14">
+        <v>0.05020154751595414</v>
+      </c>
+      <c r="Y14">
+        <v>-0.1254824463923586</v>
+      </c>
+      <c r="Z14">
+        <v>1.553599171413775</v>
+      </c>
+      <c r="AA14">
+        <v>-0.06182030036250646</v>
+      </c>
+      <c r="AB14">
+        <v>0.04609474457925845</v>
+      </c>
+      <c r="AC14">
+        <v>-0.1079150449417649</v>
+      </c>
+      <c r="AD14">
+        <v>4.08</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>4.08</v>
+      </c>
+      <c r="AG14">
+        <v>0.8200000000000003</v>
+      </c>
+      <c r="AH14">
+        <v>0.2402826855123675</v>
+      </c>
+      <c r="AI14">
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="AJ14">
+        <v>0.05976676384839652</v>
+      </c>
+      <c r="AK14">
+        <v>0.05387647831800264</v>
+      </c>
+      <c r="AL14">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AM14">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AN14">
+        <v>-5.217391304347826</v>
+      </c>
+      <c r="AO14">
+        <v>-13.64285714285714</v>
+      </c>
+      <c r="AP14">
+        <v>-1.048593350383632</v>
+      </c>
+      <c r="AQ14">
+        <v>-13.64285714285714</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>creditshelf Aktiengesellschaft (XTRA:CSQ)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G13">
-        <v>-0.9523809523809524</v>
-      </c>
-      <c r="H13">
-        <v>-0.9523809523809524</v>
-      </c>
-      <c r="I13">
-        <v>-0.5328185328185328</v>
-      </c>
-      <c r="J13">
-        <v>-0.5328185328185328</v>
-      </c>
-      <c r="K13">
-        <v>-3.71</v>
-      </c>
-      <c r="L13">
-        <v>-0.4774774774774775</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0.909</v>
-      </c>
-      <c r="V13">
-        <v>0.01611702127659575</v>
-      </c>
-      <c r="W13">
-        <v>-0.6648745519713262</v>
-      </c>
-      <c r="X13">
-        <v>0.02312377288162901</v>
-      </c>
-      <c r="Y13">
-        <v>-0.6879983248529552</v>
-      </c>
-      <c r="Z13">
-        <v>4.209100758396533</v>
-      </c>
-      <c r="AA13">
-        <v>-2.242686890574214</v>
-      </c>
-      <c r="AB13">
-        <v>0.02290276364338612</v>
-      </c>
-      <c r="AC13">
-        <v>-2.2655896542176</v>
-      </c>
-      <c r="AD13">
-        <v>1.9</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>1.9</v>
-      </c>
-      <c r="AG13">
-        <v>0.9909999999999999</v>
-      </c>
-      <c r="AH13">
-        <v>0.03259005145797599</v>
-      </c>
-      <c r="AI13">
-        <v>0.4408352668213457</v>
-      </c>
-      <c r="AJ13">
-        <v>0.01726751581258385</v>
-      </c>
-      <c r="AK13">
-        <v>0.2913848867980006</v>
-      </c>
-      <c r="AL13">
-        <v>0.096</v>
-      </c>
-      <c r="AM13">
-        <v>0.075</v>
-      </c>
-      <c r="AN13">
-        <v>-0.4773869346733668</v>
-      </c>
-      <c r="AO13">
-        <v>-43.12499999999999</v>
-      </c>
-      <c r="AP13">
-        <v>-0.2489949748743718</v>
-      </c>
-      <c r="AQ13">
-        <v>-55.2</v>
+      <c r="G15">
+        <v>-0.3049555273189327</v>
+      </c>
+      <c r="H15">
+        <v>-0.3049555273189327</v>
+      </c>
+      <c r="I15">
+        <v>-0.1575603557814485</v>
+      </c>
+      <c r="J15">
+        <v>-0.1575603557814485</v>
+      </c>
+      <c r="K15">
+        <v>0.252</v>
+      </c>
+      <c r="L15">
+        <v>0.03202033036848793</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>1.97</v>
+      </c>
+      <c r="V15">
+        <v>0.05225464190981432</v>
+      </c>
+      <c r="W15">
+        <v>0.1045643153526971</v>
+      </c>
+      <c r="X15">
+        <v>0.04862536737307842</v>
+      </c>
+      <c r="Y15">
+        <v>0.05593894797961866</v>
+      </c>
+      <c r="Z15">
+        <v>2.314025286680388</v>
+      </c>
+      <c r="AA15">
+        <v>-0.3645986474566303</v>
+      </c>
+      <c r="AB15">
+        <v>0.04791836540747734</v>
+      </c>
+      <c r="AC15">
+        <v>-0.4125170128641077</v>
+      </c>
+      <c r="AD15">
+        <v>2.83</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>2.83</v>
+      </c>
+      <c r="AG15">
+        <v>0.8600000000000001</v>
+      </c>
+      <c r="AH15">
+        <v>0.06982482112015791</v>
+      </c>
+      <c r="AI15">
+        <v>0.5173674588665448</v>
+      </c>
+      <c r="AJ15">
+        <v>0.02230290456431535</v>
+      </c>
+      <c r="AK15">
+        <v>0.2457142857142857</v>
+      </c>
+      <c r="AL15">
+        <v>0.188</v>
+      </c>
+      <c r="AM15">
+        <v>0.17</v>
+      </c>
+      <c r="AN15">
+        <v>-1.704819277108434</v>
+      </c>
+      <c r="AO15">
+        <v>-6.595744680851063</v>
+      </c>
+      <c r="AP15">
+        <v>-0.5180722891566266</v>
+      </c>
+      <c r="AQ15">
+        <v>-7.294117647058823</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EV Digital Invest AG (DB:ENGL)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>0.02270916334661355</v>
+      </c>
+      <c r="H16">
+        <v>0.02270916334661355</v>
+      </c>
+      <c r="I16">
+        <v>-1.05215269560889</v>
+      </c>
+      <c r="J16">
+        <v>-1.05215269560889</v>
+      </c>
+      <c r="K16">
+        <v>-2.65</v>
+      </c>
+      <c r="L16">
+        <v>-1.055776892430279</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>4.82</v>
+      </c>
+      <c r="V16">
+        <v>0.1928</v>
+      </c>
+      <c r="X16">
+        <v>0.04834252164649143</v>
+      </c>
+      <c r="Z16">
+        <v>3.159154702764338</v>
+      </c>
+      <c r="AA16">
+        <v>-3.323913136358999</v>
+      </c>
+      <c r="AB16">
+        <v>0.04812128738627295</v>
+      </c>
+      <c r="AC16">
+        <v>-3.372034423745272</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0.794516329891565</v>
+      </c>
+      <c r="AF16">
+        <v>0.794516329891565</v>
+      </c>
+      <c r="AG16">
+        <v>-4.025483670108436</v>
+      </c>
+      <c r="AH16">
+        <v>0.03080175335448536</v>
+      </c>
+      <c r="AI16">
+        <v>0.08430314109293992</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.1919225982041631</v>
+      </c>
+      <c r="AK16">
+        <v>-0.8742468006847605</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>-0</v>
+      </c>
+      <c r="AP16">
+        <v>1.641714384220406</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04994999999999999</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="E2">
-        <v>0.04326000000000001</v>
+        <v>-0.0377</v>
       </c>
       <c r="F2">
-        <v>0.2035</v>
+        <v>0.162</v>
       </c>
       <c r="G2">
-        <v>0.07868560384419802</v>
+        <v>0.07626371602746686</v>
       </c>
       <c r="H2">
-        <v>0.06533477628752149</v>
+        <v>0.06974036486921237</v>
       </c>
       <c r="I2">
-        <v>0.06277435687290096</v>
+        <v>0.07238197694149784</v>
       </c>
       <c r="J2">
-        <v>0.05456300391260824</v>
+        <v>0.06589457559519127</v>
       </c>
       <c r="K2">
-        <v>5612.107</v>
+        <v>7633.154</v>
       </c>
       <c r="L2">
-        <v>0.1733802447914317</v>
+        <v>0.2091734677044107</v>
       </c>
       <c r="M2">
-        <v>1262.6452</v>
+        <v>1505.2954</v>
       </c>
       <c r="N2">
-        <v>0.02112252163032059</v>
+        <v>0.02187998053427259</v>
       </c>
       <c r="O2">
-        <v>0.2249859455637606</v>
+        <v>0.1972049037658614</v>
       </c>
       <c r="P2">
-        <v>1262.6442</v>
+        <v>1505.2944</v>
       </c>
       <c r="Q2">
-        <v>0.02112250490153436</v>
+        <v>0.02187996599893252</v>
       </c>
       <c r="R2">
-        <v>0.2249857673775643</v>
+        <v>0.1972047727584167</v>
       </c>
       <c r="S2">
         <v>0.001</v>
       </c>
       <c r="T2">
-        <v>7.919881214453593e-07</v>
+        <v>6.643214348492661e-07</v>
       </c>
       <c r="U2">
-        <v>190238.85</v>
+        <v>182133.5</v>
       </c>
       <c r="V2">
-        <v>3.182465053565574</v>
+        <v>2.647372359364771</v>
       </c>
       <c r="W2">
-        <v>0.06204919144803849</v>
+        <v>0.08321578648075802</v>
       </c>
       <c r="X2">
-        <v>0.05141193991815046</v>
+        <v>0.05497330266373114</v>
       </c>
       <c r="Y2">
-        <v>0.01063725152988804</v>
+        <v>0.02824248381702688</v>
       </c>
       <c r="Z2">
-        <v>0.06595868448746389</v>
+        <v>0.07014076876592147</v>
       </c>
       <c r="AA2">
-        <v>0.0004082514267073862</v>
+        <v>0.0005240531081702158</v>
       </c>
       <c r="AB2">
-        <v>0.04691063072238714</v>
+        <v>0.04708157684297851</v>
       </c>
       <c r="AC2">
-        <v>-0.04263502182954543</v>
+        <v>-0.04275069132297118</v>
       </c>
       <c r="AD2">
-        <v>657594.21</v>
+        <v>554605.3300000001</v>
       </c>
       <c r="AE2">
-        <v>15.84326369790463</v>
+        <v>10.88172545199591</v>
       </c>
       <c r="AF2">
-        <v>657610.0532636979</v>
+        <v>554616.211725452</v>
       </c>
       <c r="AG2">
-        <v>467371.2032636979</v>
+        <v>372482.711725452</v>
       </c>
       <c r="AH2">
-        <v>0.9166737355200442</v>
+        <v>0.8896434242866599</v>
       </c>
       <c r="AI2">
-        <v>0.8836805409015575</v>
+        <v>0.8556157384874006</v>
       </c>
       <c r="AJ2">
-        <v>0.8866027106789939</v>
+        <v>0.8440950100089537</v>
       </c>
       <c r="AK2">
-        <v>0.8437325941402637</v>
+        <v>0.7991928690219681</v>
       </c>
       <c r="AL2">
-        <v>105.715</v>
+        <v>75.128</v>
       </c>
       <c r="AM2">
-        <v>8.138999999999996</v>
+        <v>23.9</v>
       </c>
       <c r="AN2">
-        <v>297.1047886430513</v>
+        <v>196.7894217299419</v>
       </c>
       <c r="AO2">
-        <v>19.1714042472686</v>
+        <v>35.11513683313811</v>
       </c>
       <c r="AP2">
-        <v>211.1609567905252</v>
+        <v>132.167243046244</v>
       </c>
       <c r="AQ2">
-        <v>249.0115493303847</v>
+        <v>110.3820083682008</v>
       </c>
     </row>
     <row r="3">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.04497153700189753</v>
+        <v>0.07452667814113598</v>
       </c>
       <c r="H3">
-        <v>0.04497153700189753</v>
+        <v>0.07452667814113598</v>
       </c>
       <c r="I3">
-        <v>0.02846299810246679</v>
+        <v>0.04440619621342513</v>
       </c>
       <c r="J3">
-        <v>0.02651248808021653</v>
+        <v>0.04221952746049132</v>
       </c>
       <c r="K3">
-        <v>0.734</v>
+        <v>1.25</v>
       </c>
       <c r="L3">
-        <v>0.01392789373814042</v>
+        <v>0.02151462994836489</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -770,10 +770,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.04813485421146283</v>
+        <v>0.04981714963548235</v>
       </c>
       <c r="AB3">
-        <v>0.04813485421146283</v>
+        <v>0.04981714963548235</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,22 +794,22 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>0.792</v>
+        <v>1.56</v>
       </c>
       <c r="AM3">
-        <v>0.7310000000000001</v>
+        <v>1.422</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>1.893939393939394</v>
+        <v>1.653846153846154</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>2.051983584131327</v>
+        <v>1.814345991561181</v>
       </c>
     </row>
     <row r="4">
@@ -820,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stock3 AG (MUN:BOG)</t>
+          <t>Stock3 AG (XTRA:BOG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,22 +829,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.1385185185185185</v>
+        <v>0.1</v>
       </c>
       <c r="H4">
-        <v>0.1385185185185185</v>
+        <v>0.1</v>
       </c>
       <c r="I4">
-        <v>0.1428865420639299</v>
+        <v>0.1080413251293042</v>
       </c>
       <c r="J4">
-        <v>0.09799094106316103</v>
+        <v>0.07432197607685199</v>
       </c>
       <c r="K4">
-        <v>1.21</v>
+        <v>0.854</v>
       </c>
       <c r="L4">
-        <v>0.08962962962962963</v>
+        <v>0.06373134328358208</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -868,67 +868,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.203914590747331</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.04853718672279859</v>
+        <v>0.05028941901115246</v>
       </c>
       <c r="Z4">
-        <v>7.802753734357315</v>
+        <v>9.597264294919892</v>
       </c>
       <c r="AA4">
-        <v>0.7645991813137673</v>
+        <v>0.713287647330262</v>
       </c>
       <c r="AB4">
-        <v>0.04810930761200346</v>
+        <v>0.04920692204844763</v>
       </c>
       <c r="AC4">
-        <v>0.7164898737017638</v>
+        <v>0.6640807252818143</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.730158410684731</v>
+        <v>1.396231216336619</v>
       </c>
       <c r="AF4">
-        <v>1.730158410684731</v>
+        <v>1.396231216336619</v>
       </c>
       <c r="AG4">
-        <v>-3.999841589315269</v>
+        <v>1.396231216336619</v>
       </c>
       <c r="AH4">
-        <v>0.05800030917921686</v>
+        <v>0.05770449140831165</v>
       </c>
       <c r="AI4">
-        <v>0.2617423521784416</v>
+        <v>1</v>
       </c>
       <c r="AJ4">
-        <v>-0.1659674397634645</v>
+        <v>0.05770449140831165</v>
       </c>
       <c r="AK4">
-        <v>-4.544456475969526</v>
+        <v>1</v>
       </c>
       <c r="AL4">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
-      <c r="AO4">
-        <v>586.6666666666666</v>
-      </c>
       <c r="AP4">
-        <v>-1.677082427385857</v>
+        <v>0.7642206985969451</v>
       </c>
       <c r="AQ4">
-        <v>880</v>
+        <v>-620</v>
       </c>
     </row>
     <row r="5">
@@ -947,113 +944,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>1.962</v>
+      </c>
       <c r="G5">
-        <v>0.5385964912280702</v>
+        <v>0.1914454277286136</v>
       </c>
       <c r="H5">
-        <v>0.5385964912280702</v>
+        <v>0.1914454277286136</v>
       </c>
       <c r="I5">
-        <v>0.5280701754385965</v>
+        <v>0.1687315634218289</v>
       </c>
       <c r="J5">
-        <v>0.5280701754385965</v>
+        <v>0.1622482816745862</v>
       </c>
       <c r="K5">
-        <v>7.5</v>
+        <v>5.86</v>
       </c>
       <c r="L5">
-        <v>0.6578947368421052</v>
+        <v>0.1728613569321534</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.519</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.02127049180327869</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.08856655290102389</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.519</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.02127049180327869</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.08856655290102389</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>14.1</v>
+        <v>10.4</v>
       </c>
       <c r="V5">
-        <v>0.5662650602409639</v>
+        <v>0.4262295081967213</v>
       </c>
       <c r="W5">
-        <v>0.3731343283582089</v>
+        <v>0.2325396825396825</v>
       </c>
       <c r="X5">
-        <v>0.05262233232034677</v>
+        <v>0.05541151373317195</v>
       </c>
       <c r="Y5">
-        <v>0.3205119960378622</v>
+        <v>0.1771281688065106</v>
       </c>
       <c r="Z5">
-        <v>0.3842264914054601</v>
+        <v>1.202127659574468</v>
       </c>
       <c r="AA5">
-        <v>0.2028985507246377</v>
+        <v>0.1950431471194494</v>
       </c>
       <c r="AB5">
-        <v>0.04687252558991987</v>
+        <v>0.04708157684297851</v>
       </c>
       <c r="AC5">
-        <v>0.1560260251347178</v>
+        <v>0.1479615702764709</v>
       </c>
       <c r="AD5">
-        <v>17.1</v>
+        <v>17.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>17.1</v>
+        <v>17.7</v>
       </c>
       <c r="AG5">
-        <v>3.000000000000002</v>
+        <v>7.299999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.4071428571428572</v>
+        <v>0.4204275534441805</v>
       </c>
       <c r="AI5">
-        <v>0.4042553191489363</v>
+        <v>0.3582995951417004</v>
       </c>
       <c r="AJ5">
-        <v>0.1075268817204302</v>
+        <v>0.2302839116719243</v>
       </c>
       <c r="AK5">
-        <v>0.1063829787234043</v>
+        <v>0.1871794871794872</v>
       </c>
       <c r="AL5">
-        <v>0.222</v>
+        <v>0.716</v>
       </c>
       <c r="AM5">
-        <v>-0.415</v>
+        <v>-0.235</v>
       </c>
       <c r="AN5">
-        <v>2.798690671031097</v>
+        <v>3.067590987868285</v>
       </c>
       <c r="AO5">
-        <v>27.11711711711711</v>
+        <v>7.988826815642458</v>
       </c>
       <c r="AP5">
-        <v>0.4909983633387892</v>
+        <v>1.265164644714038</v>
       </c>
       <c r="AQ5">
-        <v>-14.50602409638554</v>
+        <v>-24.34042553191489</v>
       </c>
     </row>
     <row r="6">
@@ -1064,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hypoport SE (XTRA:HYQ)</t>
+          <t>Deutsche Börse AG (XTRA:DB1)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1073,121 +1076,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.212</v>
+        <v>0.127</v>
       </c>
       <c r="E6">
-        <v>0.08380000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="F6">
-        <v>0.276</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G6">
-        <v>0.237160751565762</v>
+        <v>0.4344768494568029</v>
       </c>
       <c r="H6">
-        <v>0.1688935281837161</v>
+        <v>0.4032430160372478</v>
       </c>
       <c r="I6">
-        <v>0.08225469728601252</v>
+        <v>0.4253750646663217</v>
       </c>
       <c r="J6">
-        <v>0.05716004387672056</v>
+        <v>0.3134538726687753</v>
       </c>
       <c r="K6">
-        <v>28.9</v>
+        <v>1773.9</v>
       </c>
       <c r="L6">
-        <v>0.06033402922755741</v>
+        <v>0.2867789705121573</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>699.8969999999999</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.01847815296882013</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.3945526805344156</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>699.8969999999999</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.01847815296882013</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.3945526805344156</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>33.4</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>0.05090687395214144</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.1009783368273934</v>
+        <v>0.2167151269333203</v>
       </c>
       <c r="X6">
-        <v>0.04991958841705024</v>
+        <v>0.05164360206211503</v>
       </c>
       <c r="Y6">
-        <v>0.05105874841034319</v>
+        <v>0.1650715248712053</v>
       </c>
       <c r="Z6">
-        <v>2.283126787416587</v>
+        <v>0.4640812682407137</v>
       </c>
       <c r="AA6">
-        <v>0.1305036273448482</v>
+        <v>0.1454680707630884</v>
       </c>
       <c r="AB6">
-        <v>0.04746970185613153</v>
+        <v>0.04799219312784526</v>
       </c>
       <c r="AC6">
-        <v>0.08303392548871666</v>
+        <v>0.09747587763524314</v>
       </c>
       <c r="AD6">
-        <v>179.2</v>
+        <v>8970.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>179.2</v>
+        <v>8970.5</v>
       </c>
       <c r="AG6">
-        <v>145.8</v>
+        <v>8970.5</v>
       </c>
       <c r="AH6">
-        <v>0.2145337004668981</v>
+        <v>0.1914830033619724</v>
       </c>
       <c r="AI6">
-        <v>0.396547908829387</v>
+        <v>0.4738223766915625</v>
       </c>
       <c r="AJ6">
-        <v>0.1818181818181818</v>
+        <v>0.1914830033619724</v>
       </c>
       <c r="AK6">
-        <v>0.3483870967741935</v>
+        <v>0.4738223766915625</v>
       </c>
       <c r="AL6">
-        <v>3.22</v>
+        <v>62.8</v>
       </c>
       <c r="AM6">
-        <v>3.034</v>
+        <v>62.8</v>
       </c>
       <c r="AN6">
-        <v>2.552706552706552</v>
+        <v>3.214080974561089</v>
       </c>
       <c r="AO6">
-        <v>12.23602484472049</v>
+        <v>41.89808917197452</v>
       </c>
       <c r="AP6">
-        <v>2.076923076923077</v>
+        <v>3.214080974561089</v>
       </c>
       <c r="AQ6">
-        <v>12.98615688859591</v>
+        <v>41.89808917197452</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deutsche Börse AG (XTRA:DB1)</t>
+          <t>FORIS AG (XTRA:FRS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1207,124 +1213,118 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.113</v>
+        <v>-0.00733</v>
       </c>
       <c r="E7">
-        <v>0.113</v>
-      </c>
-      <c r="F7">
-        <v>0.124</v>
+        <v>-0.0377</v>
       </c>
       <c r="G7">
-        <v>0.4946183652131128</v>
+        <v>0.01588709677419355</v>
       </c>
       <c r="H7">
-        <v>0.4139861000061504</v>
+        <v>0.01588709677419355</v>
       </c>
       <c r="I7">
-        <v>0.4053139799495664</v>
+        <v>0.0625</v>
       </c>
       <c r="J7">
-        <v>0.2999150328600677</v>
+        <v>0.06236313868613139</v>
       </c>
       <c r="K7">
-        <v>1388.9</v>
+        <v>1.36</v>
       </c>
       <c r="L7">
-        <v>0.2847448592574369</v>
+        <v>0.05483870967741936</v>
       </c>
       <c r="M7">
-        <v>576.504</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.01820151925590559</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.4150795593635251</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>576.504</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.01820151925590559</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.4150795593635251</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>0.169672131147541</v>
       </c>
       <c r="W7">
-        <v>0.1768668500407498</v>
+        <v>0.09444444444444444</v>
       </c>
       <c r="X7">
-        <v>0.0491959455046638</v>
+        <v>0.05423574907535244</v>
       </c>
       <c r="Y7">
-        <v>0.127670904536086</v>
+        <v>0.040208695369092</v>
       </c>
       <c r="Z7">
-        <v>0.3639748679222756</v>
+        <v>1.650472514308532</v>
       </c>
       <c r="AA7">
-        <v>0.1091615344731481</v>
+        <v>0.102928646307471</v>
       </c>
       <c r="AB7">
-        <v>0.04694873585485441</v>
+        <v>0.04596516611356434</v>
       </c>
       <c r="AC7">
-        <v>0.06221279861829367</v>
+        <v>0.05696348019390661</v>
       </c>
       <c r="AD7">
-        <v>5143.3</v>
+        <v>6.99</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>5143.3</v>
+        <v>6.99</v>
       </c>
       <c r="AG7">
-        <v>5143.3</v>
+        <v>4.92</v>
       </c>
       <c r="AH7">
-        <v>0.1397001904027248</v>
+        <v>0.3642522146951538</v>
       </c>
       <c r="AI7">
-        <v>0.3682571277189868</v>
+        <v>0.2988456605386918</v>
       </c>
       <c r="AJ7">
-        <v>0.1397001904027248</v>
+        <v>0.2873831775700935</v>
       </c>
       <c r="AK7">
-        <v>0.3682571277189868</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AL7">
-        <v>94</v>
+        <v>0.245</v>
       </c>
       <c r="AM7">
-        <v>17.5</v>
+        <v>0.245</v>
       </c>
       <c r="AN7">
-        <v>2.422314322045872</v>
+        <v>4.017241379310345</v>
       </c>
       <c r="AO7">
-        <v>21.03191489361702</v>
+        <v>6.326530612244898</v>
       </c>
       <c r="AP7">
-        <v>2.422314322045872</v>
+        <v>2.827586206896552</v>
       </c>
       <c r="AQ7">
-        <v>112.9714285714286</v>
+        <v>6.326530612244898</v>
       </c>
     </row>
     <row r="8">
@@ -1344,121 +1344,118 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0263</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="E8">
-        <v>-0.805</v>
+        <v>0.0206</v>
       </c>
       <c r="G8">
-        <v>0.2962962962962963</v>
+        <v>0.2080645161290323</v>
       </c>
       <c r="H8">
-        <v>0.2962962962962963</v>
+        <v>0.2080645161290323</v>
       </c>
       <c r="I8">
-        <v>0.2181481481481481</v>
+        <v>0.3067741935483871</v>
       </c>
       <c r="J8">
-        <v>0.2181481481481481</v>
+        <v>0.2689670541302703</v>
       </c>
       <c r="K8">
-        <v>0.001</v>
+        <v>4.11</v>
       </c>
       <c r="L8">
-        <v>3.703703703703704e-05</v>
+        <v>0.1325806451612903</v>
       </c>
       <c r="M8">
-        <v>0.886</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.01881104033970276</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>886</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>0.886</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.01881104033970276</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>886</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>15.2</v>
+        <v>7.16</v>
       </c>
       <c r="V8">
-        <v>0.3227176220806794</v>
+        <v>0.1536480686695279</v>
       </c>
       <c r="W8">
-        <v>3.174603174603174e-05</v>
+        <v>0.15</v>
       </c>
       <c r="X8">
-        <v>0.07812926687309307</v>
+        <v>0.08404123936150004</v>
       </c>
       <c r="Y8">
-        <v>-0.07809752084134704</v>
+        <v>0.06595876063849998</v>
       </c>
       <c r="Z8">
-        <v>0.1184730144800351</v>
+        <v>0.1447245564892624</v>
       </c>
       <c r="AA8">
-        <v>0.0258446687143484</v>
+        <v>0.03892613761922679</v>
       </c>
       <c r="AB8">
-        <v>0.04777318826328403</v>
+        <v>0.04118684464974704</v>
       </c>
       <c r="AC8">
-        <v>-0.02192851954893563</v>
+        <v>-0.002260707030520254</v>
       </c>
       <c r="AD8">
-        <v>216.2</v>
+        <v>206.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>216.2</v>
+        <v>206.8</v>
       </c>
       <c r="AG8">
-        <v>201</v>
+        <v>199.64</v>
       </c>
       <c r="AH8">
-        <v>0.8211165970375996</v>
+        <v>0.8161010260457775</v>
       </c>
       <c r="AI8">
-        <v>0.8871563397620025</v>
+        <v>0.8584474885844749</v>
       </c>
       <c r="AJ8">
-        <v>0.8101571946795647</v>
+        <v>0.8107537361923327</v>
       </c>
       <c r="AK8">
-        <v>0.8796498905908097</v>
+        <v>0.8541114058355438</v>
       </c>
       <c r="AL8">
-        <v>7.22</v>
+        <v>6.29</v>
       </c>
       <c r="AM8">
-        <v>6.987</v>
+        <v>5.411</v>
       </c>
       <c r="AN8">
-        <v>35.44262295081968</v>
+        <v>21.18852459016394</v>
       </c>
       <c r="AO8">
-        <v>0.8157894736842105</v>
+        <v>1.511923688394277</v>
       </c>
       <c r="AP8">
-        <v>32.95081967213115</v>
+        <v>20.45491803278689</v>
       </c>
       <c r="AQ8">
-        <v>0.842994131959353</v>
+        <v>1.757530955461098</v>
       </c>
     </row>
     <row r="9">
@@ -1469,7 +1466,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aareal Bank AG (XTRA:ARL)</t>
+          <t>Deutsche Bank Aktiengesellschaft (XTRA:DBK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1478,13 +1475,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0244</v>
-      </c>
-      <c r="E9">
-        <v>-0.104</v>
+        <v>0.0164</v>
       </c>
       <c r="F9">
-        <v>0.5579999999999999</v>
+        <v>0.164</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1499,28 +1493,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>110.8</v>
+        <v>5634</v>
       </c>
       <c r="L9">
-        <v>0.1518640350877193</v>
+        <v>0.1959216035386905</v>
       </c>
       <c r="M9">
-        <v>94.04300000000001</v>
+        <v>633.2334</v>
       </c>
       <c r="N9">
-        <v>0.04446687786656579</v>
+        <v>0.02326891969853419</v>
       </c>
       <c r="O9">
-        <v>0.8487635379061372</v>
+        <v>0.1123949946751864</v>
       </c>
       <c r="P9">
-        <v>94.04300000000001</v>
+        <v>633.2334</v>
       </c>
       <c r="Q9">
-        <v>0.04446687786656579</v>
+        <v>0.02326891969853419</v>
       </c>
       <c r="R9">
-        <v>0.8487635379061372</v>
+        <v>0.1123949946751864</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1529,55 +1523,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>8161.4</v>
+        <v>179591.4</v>
       </c>
       <c r="V9">
-        <v>3.859000425552035</v>
+        <v>6.599301087319989</v>
       </c>
       <c r="W9">
-        <v>0.03215508735271925</v>
+        <v>0.08321578648075802</v>
       </c>
       <c r="X9">
-        <v>0.1590524667774009</v>
+        <v>0.1952628720489999</v>
       </c>
       <c r="Y9">
-        <v>-0.1268973794246817</v>
+        <v>-0.1120470855682418</v>
       </c>
       <c r="Z9">
-        <v>0.0213577511131147</v>
+        <v>0.06153405017921147</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04011676125404851</v>
+        <v>0.04275069132297118</v>
       </c>
       <c r="AC9">
-        <v>-0.04011676125404851</v>
+        <v>-0.04275069132297118</v>
       </c>
       <c r="AD9">
-        <v>35899.2</v>
+        <v>513240.9</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>35899.2</v>
+        <v>513240.9</v>
       </c>
       <c r="AG9">
-        <v>27737.8</v>
+        <v>333649.5</v>
       </c>
       <c r="AH9">
-        <v>0.9443653802141836</v>
+        <v>0.9496466493207756</v>
       </c>
       <c r="AI9">
-        <v>0.9180958421351447</v>
+        <v>0.8677671823484657</v>
       </c>
       <c r="AJ9">
-        <v>0.9291554867733907</v>
+        <v>0.9245872119961248</v>
       </c>
       <c r="AK9">
-        <v>0.8964913187935515</v>
+        <v>0.8101069153345347</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1594,7 +1588,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deutsche Bank Aktiengesellschaft (XTRA:DBK)</t>
+          <t>Linus Digital Finance AG (DB:LDF)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1602,12 +1596,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D10">
-        <v>-0.01</v>
-      </c>
-      <c r="F10">
-        <v>0.276</v>
-      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1621,91 +1609,94 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3784.1</v>
+        <v>-14.8</v>
       </c>
       <c r="L10">
-        <v>0.1502909228111285</v>
+        <v>-5.441176470588236</v>
       </c>
       <c r="M10">
-        <v>399.2912</v>
+        <v>0.001</v>
       </c>
       <c r="N10">
-        <v>0.01732125055851745</v>
+        <v>7.633587786259542e-05</v>
       </c>
       <c r="O10">
-        <v>0.1055181416981581</v>
+        <v>-6.756756756756757e-05</v>
       </c>
       <c r="P10">
-        <v>399.2912</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.01732125055851745</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.1055181416981581</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>178515.4</v>
+        <v>6.62</v>
       </c>
       <c r="V10">
-        <v>7.743997293088266</v>
+        <v>0.5053435114503817</v>
       </c>
       <c r="W10">
-        <v>0.05064326217500639</v>
+        <v>-0.5543071161048689</v>
       </c>
       <c r="X10">
-        <v>0.2120147858895722</v>
+        <v>0.1184010086258324</v>
       </c>
       <c r="Y10">
-        <v>-0.1613715237145658</v>
+        <v>-0.6727081247307013</v>
       </c>
       <c r="Z10">
-        <v>0.06268722638059539</v>
+        <v>0.01441953422783925</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04515328240504234</v>
+        <v>0.04396819801696299</v>
       </c>
       <c r="AC10">
-        <v>-0.04515328240504234</v>
+        <v>-0.04396819801696299</v>
       </c>
       <c r="AD10">
-        <v>578136.9</v>
+        <v>116.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>578136.9</v>
+        <v>116.5</v>
       </c>
       <c r="AG10">
-        <v>399621.5</v>
+        <v>109.88</v>
       </c>
       <c r="AH10">
-        <v>0.9616558187192381</v>
+        <v>0.8989197530864198</v>
       </c>
       <c r="AI10">
-        <v>0.8926396437945124</v>
+        <v>0.8872810357958872</v>
       </c>
       <c r="AJ10">
-        <v>0.9454612258726356</v>
+        <v>0.893478614408847</v>
       </c>
       <c r="AK10">
-        <v>0.8517886492693151</v>
+        <v>0.8812961180622394</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>-21.8</v>
+      </c>
+      <c r="AQ10">
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -1716,7 +1707,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Linus Digital Finance AG (DB:LDF)</t>
+          <t>Deutsche Pfandbriefbank AG (XTRA:PBB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1724,92 +1715,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D11">
+        <v>-0.0107</v>
+      </c>
+      <c r="E11">
+        <v>-0.0784</v>
+      </c>
+      <c r="F11">
+        <v>-0.0399</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
       <c r="K11">
-        <v>-14.3</v>
+        <v>136.5</v>
+      </c>
+      <c r="L11">
+        <v>0.2957746478873239</v>
       </c>
       <c r="M11">
-        <v>0.001</v>
+        <v>135.845</v>
       </c>
       <c r="N11">
-        <v>5.025125628140704e-05</v>
+        <v>0.1475293223284101</v>
       </c>
       <c r="O11">
-        <v>-6.993006993006993e-05</v>
+        <v>0.9952014652014652</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>135.845</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.1475293223284101</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>0.9952014652014652</v>
       </c>
       <c r="S11">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>7.77</v>
+        <v>1401.4</v>
       </c>
       <c r="V11">
-        <v>0.3904522613065327</v>
+        <v>1.521937445699392</v>
       </c>
       <c r="W11">
-        <v>-0.6244541484716158</v>
+        <v>0.04101439259637631</v>
       </c>
       <c r="X11">
-        <v>0.1040876889020802</v>
+        <v>0.2817342514892255</v>
       </c>
       <c r="Y11">
-        <v>-0.728541837373696</v>
+        <v>-0.2407198588928492</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>0.01339855998141912</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04535861801971307</v>
+        <v>0.04532808100894675</v>
       </c>
       <c r="AC11">
-        <v>-0.04535861801971307</v>
+        <v>-0.04532808100894675</v>
       </c>
       <c r="AD11">
-        <v>170.4</v>
+        <v>27690.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>170.4</v>
+        <v>27690.5</v>
       </c>
       <c r="AG11">
-        <v>162.63</v>
+        <v>26289.1</v>
       </c>
       <c r="AH11">
-        <v>0.8954282711508145</v>
+        <v>0.9678169115000018</v>
       </c>
       <c r="AI11">
-        <v>0.8645357686453577</v>
+        <v>0.8863654550983499</v>
       </c>
       <c r="AJ11">
-        <v>0.8909768257272777</v>
+        <v>0.9661593758154201</v>
       </c>
       <c r="AK11">
-        <v>0.858976390429409</v>
+        <v>0.8810285833017751</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-18.1</v>
-      </c>
-      <c r="AQ11">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1829,49 +1841,49 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.06619999999999999</v>
+        <v>0.0341</v>
       </c>
       <c r="E12">
-        <v>0.00272</v>
+        <v>-0.0568</v>
       </c>
       <c r="F12">
-        <v>0.131</v>
+        <v>0.162</v>
       </c>
       <c r="G12">
-        <v>0.01276993355481728</v>
+        <v>0.009192200557103064</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.01043663249280385</v>
+        <v>0.005584823250706093</v>
       </c>
       <c r="J12">
-        <v>0.007854293909782633</v>
+        <v>0.004400744844762398</v>
       </c>
       <c r="K12">
-        <v>106</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="L12">
-        <v>0.2200996677740864</v>
+        <v>0.1821727019498607</v>
       </c>
       <c r="M12">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="N12">
-        <v>0.03689998972145133</v>
+        <v>0.02780798508622028</v>
       </c>
       <c r="O12">
-        <v>0.3386792452830188</v>
+        <v>0.3649337410805301</v>
       </c>
       <c r="P12">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="Q12">
-        <v>0.03689998972145133</v>
+        <v>0.02780798508622028</v>
       </c>
       <c r="R12">
-        <v>0.3386792452830188</v>
+        <v>0.3649337410805301</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1880,67 +1892,67 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>450.7</v>
+        <v>1037.3</v>
       </c>
       <c r="V12">
-        <v>0.4632541885085826</v>
+        <v>0.8057324840764331</v>
       </c>
       <c r="W12">
-        <v>0.07274723766385287</v>
+        <v>0.07454973782202294</v>
       </c>
       <c r="X12">
-        <v>0.07296757186062892</v>
+        <v>0.07487644981524343</v>
       </c>
       <c r="Y12">
-        <v>-0.0002203341967760564</v>
+        <v>-0.0003267119932204854</v>
       </c>
       <c r="Z12">
-        <v>0.1039562388157905</v>
+        <v>0.1190828204443446</v>
       </c>
       <c r="AA12">
-        <v>0.0008165028534147723</v>
+        <v>0.0005240531081702158</v>
       </c>
       <c r="AB12">
-        <v>0.04673321942091445</v>
+        <v>0.04627033704381531</v>
       </c>
       <c r="AC12">
-        <v>-0.04591671656749968</v>
+        <v>-0.04574628393564509</v>
       </c>
       <c r="AD12">
-        <v>3684</v>
+        <v>4174.3</v>
       </c>
       <c r="AE12">
-        <v>13.31858895732833</v>
+        <v>8.962863397473845</v>
       </c>
       <c r="AF12">
-        <v>3697.318588957328</v>
+        <v>4183.262863397474</v>
       </c>
       <c r="AG12">
-        <v>3246.618588957328</v>
+        <v>3145.962863397473</v>
       </c>
       <c r="AH12">
-        <v>0.7916799863928404</v>
+        <v>0.764672027477036</v>
       </c>
       <c r="AI12">
-        <v>0.7415223932189894</v>
+        <v>0.7457909433679143</v>
       </c>
       <c r="AJ12">
-        <v>0.7694286730846207</v>
+        <v>0.7096109568136251</v>
       </c>
       <c r="AK12">
-        <v>0.71583659264926</v>
+        <v>0.688114004596285</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1.84</v>
+        <v>-25.9</v>
       </c>
       <c r="AN12">
-        <v>479.0637191157347</v>
+        <v>869.6458333333334</v>
       </c>
       <c r="AP12">
-        <v>422.1870726862585</v>
+        <v>655.4089298744736</v>
       </c>
       <c r="AQ12">
         <v>-0</v>
@@ -1954,7 +1966,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deutsche Pfandbriefbank AG (XTRA:PBB)</t>
+          <t>Hypoport SE (XTRA:HYQ)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1963,112 +1975,118 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.091</v>
-      </c>
-      <c r="E13">
-        <v>0.0866</v>
+        <v>0.0789</v>
       </c>
       <c r="F13">
-        <v>0.0177</v>
+        <v>0.247</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.2072911122937733</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.1011176157530601</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>-0.01987759446514103</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>-0.01987759446514103</v>
       </c>
       <c r="K13">
-        <v>202</v>
+        <v>-2.97</v>
       </c>
       <c r="L13">
-        <v>0.417873396772859</v>
+        <v>-0.007903139968068122</v>
       </c>
       <c r="M13">
-        <v>156.02</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.1493300153139357</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.7723762376237623</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>156.02</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.1493300153139357</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.7723762376237623</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>3025.1</v>
+        <v>71</v>
       </c>
       <c r="V13">
-        <v>2.895386676875957</v>
+        <v>0.05433119069482706</v>
       </c>
       <c r="W13">
-        <v>0.05135114523222412</v>
+        <v>-0.01093922651933702</v>
       </c>
       <c r="X13">
-        <v>0.261659816255382</v>
+        <v>0.05085875419430071</v>
       </c>
       <c r="Y13">
-        <v>-0.2103086710231579</v>
+        <v>-0.06179798071363773</v>
       </c>
       <c r="Z13">
-        <v>0.01334264429459808</v>
+        <v>1.950181629475869</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>-0.03876491956408926</v>
       </c>
       <c r="AB13">
-        <v>0.04641696951678301</v>
+        <v>0.04926522630695893</v>
       </c>
       <c r="AC13">
-        <v>-0.04641696951678301</v>
+        <v>-0.08803014587104818</v>
       </c>
       <c r="AD13">
-        <v>34141</v>
+        <v>176.5</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>34141</v>
+        <v>176.5</v>
       </c>
       <c r="AG13">
-        <v>31115.9</v>
+        <v>105.5</v>
       </c>
       <c r="AH13">
-        <v>0.9703062030705568</v>
+        <v>0.1189914380098429</v>
       </c>
       <c r="AI13">
-        <v>0.9111288432952329</v>
+        <v>0.3416569879984514</v>
       </c>
       <c r="AJ13">
-        <v>0.9675131449253281</v>
+        <v>0.0747008425971819</v>
       </c>
       <c r="AK13">
-        <v>0.9033240434302967</v>
+        <v>0.2367594254937163</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1.92</v>
+      </c>
+      <c r="AN13">
+        <v>44.57070707070707</v>
+      </c>
+      <c r="AO13">
+        <v>-2.312693498452012</v>
+      </c>
+      <c r="AP13">
+        <v>26.64141414141414</v>
+      </c>
+      <c r="AQ13">
+        <v>-3.890625</v>
       </c>
     </row>
     <row r="14">
@@ -2079,7 +2097,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FORIS AG (XTRA:FRS)</t>
+          <t>EV Digital Invest AG (DB:ENGL)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2087,26 +2105,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.0337</v>
-      </c>
       <c r="G14">
-        <v>-0.05958333333333333</v>
+        <v>-0.777542372881356</v>
       </c>
       <c r="H14">
-        <v>-0.05958333333333333</v>
+        <v>-0.777542372881356</v>
       </c>
       <c r="I14">
-        <v>-0.03979166666666666</v>
+        <v>-0.5325267304315866</v>
       </c>
       <c r="J14">
-        <v>-0.03979166666666666</v>
+        <v>-0.5325267304315866</v>
       </c>
       <c r="K14">
-        <v>-1.34</v>
+        <v>-2.3</v>
       </c>
       <c r="L14">
-        <v>-0.05583333333333334</v>
+        <v>-0.4872881355932203</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2130,73 +2145,73 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="V14">
-        <v>0.2527131782945736</v>
+        <v>0.1470588235294118</v>
       </c>
       <c r="W14">
-        <v>-0.07528089887640449</v>
+        <v>-0.2665121668597914</v>
       </c>
       <c r="X14">
-        <v>0.05020154751595414</v>
+        <v>0.05001472470920218</v>
       </c>
       <c r="Y14">
-        <v>-0.1254824463923586</v>
+        <v>-0.3165268915689936</v>
       </c>
       <c r="Z14">
-        <v>1.553599171413775</v>
+        <v>1.089407377706979</v>
       </c>
       <c r="AA14">
-        <v>-0.06182030036250646</v>
+        <v>-0.5801385489583464</v>
       </c>
       <c r="AB14">
-        <v>0.04609474457925845</v>
+        <v>0.04965461877121042</v>
       </c>
       <c r="AC14">
-        <v>-0.1079150449417649</v>
+        <v>-0.6297931677295568</v>
       </c>
       <c r="AD14">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>0.5226308381854461</v>
       </c>
       <c r="AF14">
-        <v>4.08</v>
+        <v>0.5226308381854461</v>
       </c>
       <c r="AG14">
-        <v>0.8200000000000003</v>
+        <v>-2.477369161814554</v>
       </c>
       <c r="AH14">
-        <v>0.2402826855123675</v>
+        <v>0.02497921232886276</v>
       </c>
       <c r="AI14">
-        <v>0.2207792207792208</v>
+        <v>0.07226012911182482</v>
       </c>
       <c r="AJ14">
-        <v>0.05976676384839652</v>
+        <v>-0.1382257540302812</v>
       </c>
       <c r="AK14">
-        <v>0.05387647831800264</v>
+        <v>-0.5853024410880626</v>
       </c>
       <c r="AL14">
-        <v>0.07000000000000001</v>
+        <v>0.002</v>
       </c>
       <c r="AM14">
-        <v>0.07000000000000001</v>
+        <v>-0.229</v>
       </c>
       <c r="AN14">
-        <v>-5.217391304347826</v>
+        <v>-0</v>
       </c>
       <c r="AO14">
-        <v>-13.64285714285714</v>
+        <v>-1265</v>
       </c>
       <c r="AP14">
-        <v>-1.048593350383632</v>
+        <v>1.036990021688805</v>
       </c>
       <c r="AQ14">
-        <v>-13.64285714285714</v>
+        <v>11.04803493449782</v>
       </c>
     </row>
     <row r="15">
@@ -2215,23 +2230,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D15">
+        <v>0.175</v>
+      </c>
       <c r="G15">
-        <v>-0.3049555273189327</v>
+        <v>-0.4819494584837545</v>
       </c>
       <c r="H15">
-        <v>-0.3049555273189327</v>
+        <v>-0.4819494584837545</v>
       </c>
       <c r="I15">
-        <v>-0.1575603557814485</v>
+        <v>-0.6624548736462094</v>
       </c>
       <c r="J15">
-        <v>-0.1575603557814485</v>
+        <v>-0.6624548736462094</v>
       </c>
       <c r="K15">
-        <v>0.252</v>
+        <v>-2.71</v>
       </c>
       <c r="L15">
-        <v>0.03202033036848793</v>
+        <v>-0.4891696750902527</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2240,7 +2258,7 @@
         <v>-0</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2249,192 +2267,79 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>1.97</v>
+        <v>3.15</v>
       </c>
       <c r="V15">
-        <v>0.05225464190981432</v>
+        <v>0.4538904899135446</v>
       </c>
       <c r="W15">
-        <v>0.1045643153526971</v>
+        <v>-1.026515151515151</v>
       </c>
       <c r="X15">
-        <v>0.04862536737307842</v>
+        <v>0.05497330266373114</v>
       </c>
       <c r="Y15">
-        <v>0.05593894797961866</v>
+        <v>-1.081488454178883</v>
       </c>
       <c r="Z15">
-        <v>2.314025286680388</v>
+        <v>1.582857142857143</v>
       </c>
       <c r="AA15">
-        <v>-0.3645986474566303</v>
+        <v>-1.048571428571428</v>
       </c>
       <c r="AB15">
-        <v>0.04791836540747734</v>
+        <v>0.04720999658776288</v>
       </c>
       <c r="AC15">
-        <v>-0.4125170128641077</v>
+        <v>-1.095781425159191</v>
       </c>
       <c r="AD15">
-        <v>2.83</v>
+        <v>4.64</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>2.83</v>
+        <v>4.64</v>
       </c>
       <c r="AG15">
-        <v>0.8600000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="AH15">
-        <v>0.06982482112015791</v>
+        <v>0.4006908462867012</v>
       </c>
       <c r="AI15">
-        <v>0.5173674588665448</v>
+        <v>0.9213661636219221</v>
       </c>
       <c r="AJ15">
-        <v>0.02230290456431535</v>
+        <v>0.1767497034400949</v>
       </c>
       <c r="AK15">
-        <v>0.2457142857142857</v>
+        <v>0.7900318133616119</v>
       </c>
       <c r="AL15">
-        <v>0.188</v>
+        <v>0.285</v>
       </c>
       <c r="AM15">
-        <v>0.17</v>
+        <v>0.268</v>
       </c>
       <c r="AN15">
-        <v>-1.704819277108434</v>
+        <v>-1.372781065088757</v>
       </c>
       <c r="AO15">
-        <v>-6.595744680851063</v>
+        <v>-12.87719298245614</v>
       </c>
       <c r="AP15">
-        <v>-0.5180722891566266</v>
+        <v>-0.4408284023668638</v>
       </c>
       <c r="AQ15">
-        <v>-7.294117647058823</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>EV Digital Invest AG (DB:ENGL)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G16">
-        <v>0.02270916334661355</v>
-      </c>
-      <c r="H16">
-        <v>0.02270916334661355</v>
-      </c>
-      <c r="I16">
-        <v>-1.05215269560889</v>
-      </c>
-      <c r="J16">
-        <v>-1.05215269560889</v>
-      </c>
-      <c r="K16">
-        <v>-2.65</v>
-      </c>
-      <c r="L16">
-        <v>-1.055776892430279</v>
-      </c>
-      <c r="M16">
-        <v>-0</v>
-      </c>
-      <c r="N16">
-        <v>-0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>-0</v>
-      </c>
-      <c r="Q16">
-        <v>-0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>4.82</v>
-      </c>
-      <c r="V16">
-        <v>0.1928</v>
-      </c>
-      <c r="X16">
-        <v>0.04834252164649143</v>
-      </c>
-      <c r="Z16">
-        <v>3.159154702764338</v>
-      </c>
-      <c r="AA16">
-        <v>-3.323913136358999</v>
-      </c>
-      <c r="AB16">
-        <v>0.04812128738627295</v>
-      </c>
-      <c r="AC16">
-        <v>-3.372034423745272</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0.794516329891565</v>
-      </c>
-      <c r="AF16">
-        <v>0.794516329891565</v>
-      </c>
-      <c r="AG16">
-        <v>-4.025483670108436</v>
-      </c>
-      <c r="AH16">
-        <v>0.03080175335448536</v>
-      </c>
-      <c r="AI16">
-        <v>0.08430314109293992</v>
-      </c>
-      <c r="AJ16">
-        <v>-0.1919225982041631</v>
-      </c>
-      <c r="AK16">
-        <v>-0.8742468006847605</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>-0</v>
-      </c>
-      <c r="AP16">
-        <v>1.641714384220406</v>
+        <v>-13.69402985074627</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0258</v>
+        <v>0.06760000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.0916</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F2">
-        <v>0.1735</v>
+        <v>0.215</v>
       </c>
       <c r="G2">
-        <v>0.08439738399252569</v>
+        <v>0.08457300055458687</v>
       </c>
       <c r="H2">
-        <v>0.07803206963866587</v>
+        <v>0.07710030434888955</v>
       </c>
       <c r="I2">
-        <v>0.08000082535789589</v>
+        <v>0.07936607656518518</v>
       </c>
       <c r="J2">
-        <v>0.0674810686539719</v>
+        <v>0.06898421432742617</v>
       </c>
       <c r="K2">
-        <v>7230.900000000001</v>
+        <v>7269.294000000001</v>
       </c>
       <c r="L2">
-        <v>0.1830825439989062</v>
+        <v>0.1814336195454185</v>
       </c>
       <c r="M2">
-        <v>1856.2538</v>
+        <v>1857.3986</v>
       </c>
       <c r="N2">
-        <v>0.0240786105843194</v>
+        <v>0.02369746275946152</v>
       </c>
       <c r="O2">
-        <v>0.2567113084125074</v>
+        <v>0.2555129287658471</v>
       </c>
       <c r="P2">
-        <v>1794.2538</v>
+        <v>1795.3986</v>
       </c>
       <c r="Q2">
-        <v>0.02327437042264118</v>
+        <v>0.02290644100942541</v>
       </c>
       <c r="R2">
-        <v>0.2481369953947641</v>
+        <v>0.2469839024257376</v>
       </c>
       <c r="S2">
         <v>62</v>
       </c>
       <c r="T2">
-        <v>0.03340060502502405</v>
+        <v>0.03338001869927112</v>
       </c>
       <c r="U2">
-        <v>161273.4</v>
+        <v>161402.148</v>
       </c>
       <c r="V2">
-        <v>2.091976536941864</v>
+        <v>2.059235638234623</v>
       </c>
       <c r="W2">
-        <v>0.0655239871939623</v>
+        <v>0.06585077532855851</v>
       </c>
       <c r="X2">
-        <v>0.1385386636291951</v>
+        <v>0.06303314900685469</v>
       </c>
       <c r="Y2">
-        <v>-0.07301467643523279</v>
+        <v>0.00281762632170382</v>
       </c>
       <c r="Z2">
-        <v>0.08534871813248369</v>
+        <v>0.08647524802836816</v>
       </c>
       <c r="AA2">
-        <v>0.0004263693820487539</v>
+        <v>0.0008527387640975078</v>
       </c>
       <c r="AB2">
-        <v>0.04901559986648061</v>
+        <v>0.05121319176475958</v>
       </c>
       <c r="AC2">
-        <v>-0.04691031897007043</v>
+        <v>-0.04593953135988812</v>
       </c>
       <c r="AD2">
-        <v>551631.5</v>
+        <v>552042.872</v>
       </c>
       <c r="AE2">
-        <v>14.21701121146782</v>
+        <v>21.20443795004811</v>
       </c>
       <c r="AF2">
-        <v>551645.7170112114</v>
+        <v>552064.07643795</v>
       </c>
       <c r="AG2">
-        <v>390372.3170112114</v>
+        <v>390661.92843795</v>
       </c>
       <c r="AH2">
-        <v>0.8773869111363035</v>
+        <v>0.8756754362739146</v>
       </c>
       <c r="AI2">
-        <v>0.8435684802208903</v>
+        <v>0.8429551723743226</v>
       </c>
       <c r="AJ2">
-        <v>0.835085810524732</v>
+        <v>0.8328940433552022</v>
       </c>
       <c r="AK2">
-        <v>0.792361256980716</v>
+        <v>0.7915940640636054</v>
       </c>
       <c r="AL2">
-        <v>227.1</v>
+        <v>246.966</v>
       </c>
       <c r="AM2">
-        <v>126.5</v>
+        <v>143.135</v>
       </c>
       <c r="AN2">
-        <v>164.0539776951673</v>
+        <v>162.9564594672859</v>
       </c>
       <c r="AO2">
-        <v>13.89123734037869</v>
+        <v>12.85593968400509</v>
       </c>
       <c r="AP2">
-        <v>116.0958563602116</v>
+        <v>115.3187332648153</v>
       </c>
       <c r="AQ2">
-        <v>24.93833992094861</v>
+        <v>22.1817165612883</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deutsche Börse AG (XTRA:DB1)</t>
+          <t>Stock3 AG (XTRA:BOG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,125 +724,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.16</v>
-      </c>
-      <c r="E3">
-        <v>0.147</v>
-      </c>
-      <c r="F3">
-        <v>0.0599</v>
-      </c>
       <c r="G3">
-        <v>0.4332500260335312</v>
+        <v>0.1</v>
       </c>
       <c r="H3">
-        <v>0.4011636988441112</v>
+        <v>0.1</v>
       </c>
       <c r="I3">
-        <v>0.4106399041966052</v>
+        <v>0.108692349169005</v>
       </c>
       <c r="J3">
-        <v>0.3040595704527218</v>
+        <v>0.07476981761383973</v>
       </c>
       <c r="K3">
-        <v>2061.5</v>
+        <v>0.854</v>
       </c>
       <c r="L3">
-        <v>0.268340622722066</v>
+        <v>0.06373134328358208</v>
       </c>
       <c r="M3">
-        <v>777.6160000000001</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.01841339300513841</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.3772088285229203</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>777.6160000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01841339300513841</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.3772088285229203</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
         <v>0</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
-      <c r="W3">
-        <v>0.2190940781362921</v>
-      </c>
       <c r="X3">
-        <v>0.05780479276782492</v>
-      </c>
-      <c r="Y3">
-        <v>0.1612892853684672</v>
+        <v>0.05652625460825225</v>
       </c>
       <c r="Z3">
-        <v>0.4179828832897163</v>
+        <v>9.906753747349899</v>
       </c>
       <c r="AA3">
-        <v>0.1270916959496613</v>
+        <v>0.7407261708345754</v>
       </c>
       <c r="AB3">
-        <v>0.05398911856357488</v>
+        <v>0.05577566885610939</v>
       </c>
       <c r="AC3">
-        <v>0.07310257738608639</v>
+        <v>0.684950501978466</v>
       </c>
       <c r="AD3">
-        <v>9462.6</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.352612605676664</v>
       </c>
       <c r="AF3">
-        <v>9462.6</v>
+        <v>1.352612605676664</v>
       </c>
       <c r="AG3">
-        <v>9462.6</v>
+        <v>1.352612605676664</v>
       </c>
       <c r="AH3">
-        <v>0.1830516737081573</v>
+        <v>0.04671815369820754</v>
       </c>
       <c r="AI3">
-        <v>0.4462543328067156</v>
+        <v>1</v>
       </c>
       <c r="AJ3">
-        <v>0.1830516737081573</v>
+        <v>0.04671815369820754</v>
       </c>
       <c r="AK3">
-        <v>0.4462543328067156</v>
+        <v>1</v>
       </c>
       <c r="AL3">
-        <v>227.1</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>164.2</v>
+        <v>-0.002</v>
       </c>
       <c r="AN3">
-        <v>2.820699317375623</v>
-      </c>
-      <c r="AO3">
-        <v>13.89123734037869</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.820699317375623</v>
+        <v>0.7403462537912773</v>
       </c>
       <c r="AQ3">
-        <v>19.21254567600487</v>
+        <v>-620</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deutsche Bank Aktiengesellschaft (XTRA:DBK)</t>
+          <t>Deutsche Börse AG (XTRA:DB1)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,46 +841,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0401</v>
+        <v>0.16</v>
+      </c>
+      <c r="E4">
+        <v>0.147</v>
       </c>
       <c r="F4">
-        <v>0.132</v>
+        <v>0.0599</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.4332500260335312</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.4011636988441112</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.4106399041966052</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.3040595704527218</v>
       </c>
       <c r="K4">
-        <v>4976.6</v>
+        <v>2061.5</v>
       </c>
       <c r="L4">
-        <v>0.161486168573051</v>
+        <v>0.268340622722066</v>
       </c>
       <c r="M4">
-        <v>975.8378</v>
+        <v>777.6160000000001</v>
       </c>
       <c r="N4">
-        <v>0.02913948967556027</v>
+        <v>0.01841339300513841</v>
       </c>
       <c r="O4">
-        <v>0.1960852389181369</v>
+        <v>0.3772088285229203</v>
       </c>
       <c r="P4">
-        <v>975.8378</v>
+        <v>777.6160000000001</v>
       </c>
       <c r="Q4">
-        <v>0.02913948967556027</v>
+        <v>0.01841339300513841</v>
       </c>
       <c r="R4">
-        <v>0.1960852389181369</v>
+        <v>0.3772088285229203</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -910,61 +892,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>157295.3</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>4.696994490646042</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>0.06519719905936606</v>
+        <v>0.2190940781362921</v>
       </c>
       <c r="X4">
-        <v>0.1670682203380742</v>
+        <v>0.05779707475342771</v>
       </c>
       <c r="Y4">
-        <v>-0.1018710212787081</v>
+        <v>0.1612970033828644</v>
       </c>
       <c r="Z4">
-        <v>0.0751681175469107</v>
+        <v>0.4179828832897163</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.1270916959496613</v>
       </c>
       <c r="AB4">
-        <v>0.04594432452300347</v>
+        <v>0.05398281334463077</v>
       </c>
       <c r="AC4">
-        <v>-0.04594432452300347</v>
+        <v>0.0731088826050305</v>
       </c>
       <c r="AD4">
-        <v>511229.1</v>
+        <v>9462.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>511229.1</v>
+        <v>9462.6</v>
       </c>
       <c r="AG4">
-        <v>353933.8</v>
+        <v>9462.6</v>
       </c>
       <c r="AH4">
-        <v>0.9385213549185853</v>
+        <v>0.1830516737081573</v>
       </c>
       <c r="AI4">
-        <v>0.8570253892730736</v>
+        <v>0.4462543328067156</v>
       </c>
       <c r="AJ4">
-        <v>0.913560732048723</v>
+        <v>0.1830516737081573</v>
       </c>
       <c r="AK4">
-        <v>0.8058227714377565</v>
+        <v>0.4462543328067156</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>227.1</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>164.2</v>
+      </c>
+      <c r="AN4">
+        <v>2.820699317375623</v>
+      </c>
+      <c r="AO4">
+        <v>13.89123734037869</v>
+      </c>
+      <c r="AP4">
+        <v>2.820699317375623</v>
+      </c>
+      <c r="AQ4">
+        <v>19.21254567600487</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grenke AG (XTRA:GLJ)</t>
+          <t>FORIS AG (XTRA:FRS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,121 +978,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0115</v>
-      </c>
-      <c r="E5">
-        <v>-0.0916</v>
-      </c>
-      <c r="F5">
-        <v>0.215</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="G5">
-        <v>0.008329083800781916</v>
+        <v>0.05853658536585366</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.05853658536585366</v>
       </c>
       <c r="I5">
-        <v>0.008425289406266254</v>
+        <v>0.09303135888501742</v>
       </c>
       <c r="J5">
-        <v>0.006598567366854544</v>
+        <v>0.09295415443780994</v>
       </c>
       <c r="K5">
-        <v>94.7</v>
+        <v>2.4</v>
       </c>
       <c r="L5">
-        <v>0.1609722930477648</v>
+        <v>0.08362369337979093</v>
       </c>
       <c r="M5">
-        <v>102.8</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.1457535800368638</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>1.085533262935586</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>40.8</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.0578477243726074</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.4308342133051742</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>62</v>
-      </c>
-      <c r="T5">
-        <v>0.603112840466926</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1387.2</v>
+        <v>1.65</v>
       </c>
       <c r="V5">
-        <v>1.966822628668652</v>
+        <v>0.1352459016393443</v>
       </c>
       <c r="W5">
-        <v>0.06585077532855851</v>
+        <v>0.1463414634146342</v>
       </c>
       <c r="X5">
-        <v>0.110009106920316</v>
+        <v>0.05879456505431377</v>
       </c>
       <c r="Y5">
-        <v>-0.04415833159175753</v>
+        <v>0.0875468983603204</v>
       </c>
       <c r="Z5">
-        <v>0.1292308946303898</v>
+        <v>1.354476379253386</v>
       </c>
       <c r="AA5">
-        <v>0.0008527387640975078</v>
+        <v>0.1259042065394849</v>
       </c>
       <c r="AB5">
-        <v>0.04872905218123491</v>
+        <v>0.0534620586190625</v>
       </c>
       <c r="AC5">
-        <v>-0.0478763134171374</v>
+        <v>0.07244214792042236</v>
       </c>
       <c r="AD5">
-        <v>5212.6</v>
+        <v>4.41</v>
       </c>
       <c r="AE5">
-        <v>14.21701121146782</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>5226.817011211469</v>
+        <v>4.41</v>
       </c>
       <c r="AG5">
-        <v>3839.617011211469</v>
+        <v>2.76</v>
       </c>
       <c r="AH5">
-        <v>0.8811048402000482</v>
+        <v>0.2655027092113185</v>
       </c>
       <c r="AI5">
-        <v>0.7812743786771196</v>
+        <v>0.1924923614142296</v>
       </c>
       <c r="AJ5">
-        <v>0.8448156482813315</v>
+        <v>0.1844919786096257</v>
       </c>
       <c r="AK5">
-        <v>0.7240575334469161</v>
+        <v>0.1298212605832549</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.363</v>
       </c>
       <c r="AM5">
-        <v>-37.7</v>
+        <v>0.363</v>
       </c>
       <c r="AN5">
-        <v>668.2820512820514</v>
+        <v>1.541958041958042</v>
+      </c>
+      <c r="AO5">
+        <v>7.355371900826446</v>
       </c>
       <c r="AP5">
-        <v>492.2585911809575</v>
+        <v>0.9650349650349651</v>
       </c>
       <c r="AQ5">
-        <v>-0</v>
+        <v>7.355371900826446</v>
       </c>
     </row>
     <row r="6">
@@ -1109,118 +1097,987 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>ALBIS Leasing AG (XTRA:ALG)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.118</v>
+      </c>
+      <c r="E6">
+        <v>0.143</v>
+      </c>
+      <c r="G6">
+        <v>0.4246913580246913</v>
+      </c>
+      <c r="H6">
+        <v>0.4246913580246913</v>
+      </c>
+      <c r="I6">
+        <v>0.4666666666666666</v>
+      </c>
+      <c r="J6">
+        <v>0.4666666666666666</v>
+      </c>
+      <c r="K6">
+        <v>4.76</v>
+      </c>
+      <c r="L6">
+        <v>0.1175308641975309</v>
+      </c>
+      <c r="M6">
+        <v>1.1448</v>
+      </c>
+      <c r="N6">
+        <v>0.01904825291181364</v>
+      </c>
+      <c r="O6">
+        <v>0.2405042016806723</v>
+      </c>
+      <c r="P6">
+        <v>1.1448</v>
+      </c>
+      <c r="Q6">
+        <v>0.01904825291181364</v>
+      </c>
+      <c r="R6">
+        <v>0.2405042016806723</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>12.5</v>
+      </c>
+      <c r="V6">
+        <v>0.2079866888519135</v>
+      </c>
+      <c r="W6">
+        <v>0.1395894428152493</v>
+      </c>
+      <c r="X6">
+        <v>0.08001399211713264</v>
+      </c>
+      <c r="Y6">
+        <v>0.05957545069811662</v>
+      </c>
+      <c r="Z6">
+        <v>0.1849821869005207</v>
+      </c>
+      <c r="AA6">
+        <v>0.08632502055357631</v>
+      </c>
+      <c r="AB6">
+        <v>0.04969182495627057</v>
+      </c>
+      <c r="AC6">
+        <v>0.03663319559730574</v>
+      </c>
+      <c r="AD6">
+        <v>197.4</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>197.4</v>
+      </c>
+      <c r="AG6">
+        <v>184.9</v>
+      </c>
+      <c r="AH6">
+        <v>0.7666019417475728</v>
+      </c>
+      <c r="AI6">
+        <v>0.8425096030729834</v>
+      </c>
+      <c r="AJ6">
+        <v>0.7546938775510205</v>
+      </c>
+      <c r="AK6">
+        <v>0.8336339044183949</v>
+      </c>
+      <c r="AL6">
+        <v>14.1</v>
+      </c>
+      <c r="AM6">
+        <v>13.864</v>
+      </c>
+      <c r="AN6">
+        <v>10.44444444444445</v>
+      </c>
+      <c r="AO6">
+        <v>1.340425531914893</v>
+      </c>
+      <c r="AP6">
+        <v>9.783068783068783</v>
+      </c>
+      <c r="AQ6">
+        <v>1.363242931332949</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DF Deutsche Forfait AG (XTRA:DFTK)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.09539999999999998</v>
+      </c>
+      <c r="G7">
+        <v>0.4022517911975435</v>
+      </c>
+      <c r="H7">
+        <v>0.4022517911975435</v>
+      </c>
+      <c r="I7">
+        <v>0.4237461617195497</v>
+      </c>
+      <c r="J7">
+        <v>0.2118730808597748</v>
+      </c>
+      <c r="K7">
+        <v>1.27</v>
+      </c>
+      <c r="L7">
+        <v>0.1299897645854657</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>-0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>47.4</v>
+      </c>
+      <c r="V7">
+        <v>2.590163934426229</v>
+      </c>
+      <c r="W7">
+        <v>0.04006309148264985</v>
+      </c>
+      <c r="X7">
+        <v>0.06303314900685469</v>
+      </c>
+      <c r="Y7">
+        <v>-0.02297005752420485</v>
+      </c>
+      <c r="Z7">
+        <v>0.2505128205128205</v>
+      </c>
+      <c r="AA7">
+        <v>0.05307692307692307</v>
+      </c>
+      <c r="AB7">
+        <v>0.05121319176475958</v>
+      </c>
+      <c r="AC7">
+        <v>0.00186373131216349</v>
+      </c>
+      <c r="AD7">
+        <v>17.3</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>17.3</v>
+      </c>
+      <c r="AG7">
+        <v>-30.1</v>
+      </c>
+      <c r="AH7">
+        <v>0.4859550561797753</v>
+      </c>
+      <c r="AI7">
+        <v>0.3473895582329318</v>
+      </c>
+      <c r="AJ7">
+        <v>2.550847457627119</v>
+      </c>
+      <c r="AK7">
+        <v>-12.54166666666666</v>
+      </c>
+      <c r="AL7">
+        <v>0.844</v>
+      </c>
+      <c r="AM7">
+        <v>0.629</v>
+      </c>
+      <c r="AN7">
+        <v>4.119047619047619</v>
+      </c>
+      <c r="AO7">
+        <v>4.90521327014218</v>
+      </c>
+      <c r="AP7">
+        <v>-7.166666666666666</v>
+      </c>
+      <c r="AQ7">
+        <v>6.581875993640699</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Aktiengesellschaft (XTRA:DBK)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0401</v>
+      </c>
+      <c r="F8">
+        <v>0.132</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>4976.6</v>
+      </c>
+      <c r="L8">
+        <v>0.161486168573051</v>
+      </c>
+      <c r="M8">
+        <v>975.8378</v>
+      </c>
+      <c r="N8">
+        <v>0.02913948967556027</v>
+      </c>
+      <c r="O8">
+        <v>0.1960852389181369</v>
+      </c>
+      <c r="P8">
+        <v>975.8378</v>
+      </c>
+      <c r="Q8">
+        <v>0.02913948967556027</v>
+      </c>
+      <c r="R8">
+        <v>0.1960852389181369</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>157295.3</v>
+      </c>
+      <c r="V8">
+        <v>4.696994490646042</v>
+      </c>
+      <c r="W8">
+        <v>0.06519719905936606</v>
+      </c>
+      <c r="X8">
+        <v>0.1669902556544187</v>
+      </c>
+      <c r="Y8">
+        <v>-0.1017930565950526</v>
+      </c>
+      <c r="Z8">
+        <v>0.0751681175469107</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.04593953135988812</v>
+      </c>
+      <c r="AC8">
+        <v>-0.04593953135988812</v>
+      </c>
+      <c r="AD8">
+        <v>511229.1</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>511229.1</v>
+      </c>
+      <c r="AG8">
+        <v>353933.8</v>
+      </c>
+      <c r="AH8">
+        <v>0.9385213549185853</v>
+      </c>
+      <c r="AI8">
+        <v>0.8570253892730736</v>
+      </c>
+      <c r="AJ8">
+        <v>0.913560732048723</v>
+      </c>
+      <c r="AK8">
+        <v>0.8058227714377565</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grenke AG (XTRA:GLJ)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0115</v>
+      </c>
+      <c r="E9">
+        <v>-0.0916</v>
+      </c>
+      <c r="F9">
+        <v>0.215</v>
+      </c>
+      <c r="G9">
+        <v>0.008329083800781916</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0.008425289406266254</v>
+      </c>
+      <c r="J9">
+        <v>0.006598567366854544</v>
+      </c>
+      <c r="K9">
+        <v>94.7</v>
+      </c>
+      <c r="L9">
+        <v>0.1609722930477648</v>
+      </c>
+      <c r="M9">
+        <v>102.8</v>
+      </c>
+      <c r="N9">
+        <v>0.1457535800368638</v>
+      </c>
+      <c r="O9">
+        <v>1.085533262935586</v>
+      </c>
+      <c r="P9">
+        <v>40.8</v>
+      </c>
+      <c r="Q9">
+        <v>0.0578477243726074</v>
+      </c>
+      <c r="R9">
+        <v>0.4308342133051742</v>
+      </c>
+      <c r="S9">
+        <v>62</v>
+      </c>
+      <c r="T9">
+        <v>0.603112840466926</v>
+      </c>
+      <c r="U9">
+        <v>1387.2</v>
+      </c>
+      <c r="V9">
+        <v>1.966822628668652</v>
+      </c>
+      <c r="W9">
+        <v>0.06585077532855851</v>
+      </c>
+      <c r="X9">
+        <v>0.1099678261734321</v>
+      </c>
+      <c r="Y9">
+        <v>-0.04411705084487358</v>
+      </c>
+      <c r="Z9">
+        <v>0.1292308946303898</v>
+      </c>
+      <c r="AA9">
+        <v>0.0008527387640975078</v>
+      </c>
+      <c r="AB9">
+        <v>0.04872414410023748</v>
+      </c>
+      <c r="AC9">
+        <v>-0.04787140533613998</v>
+      </c>
+      <c r="AD9">
+        <v>5212.6</v>
+      </c>
+      <c r="AE9">
+        <v>14.21701121146782</v>
+      </c>
+      <c r="AF9">
+        <v>5226.817011211469</v>
+      </c>
+      <c r="AG9">
+        <v>3839.617011211469</v>
+      </c>
+      <c r="AH9">
+        <v>0.8811048402000482</v>
+      </c>
+      <c r="AI9">
+        <v>0.7812743786771196</v>
+      </c>
+      <c r="AJ9">
+        <v>0.8448156482813315</v>
+      </c>
+      <c r="AK9">
+        <v>0.7240575334469161</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-37.7</v>
+      </c>
+      <c r="AN9">
+        <v>668.2820512820514</v>
+      </c>
+      <c r="AP9">
+        <v>492.2585911809575</v>
+      </c>
+      <c r="AQ9">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Deutsche Pfandbriefbank AG (XTRA:PBB)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="D10">
         <v>-0.04849999999999999</v>
       </c>
-      <c r="E6">
+      <c r="E10">
         <v>-0.148</v>
       </c>
-      <c r="F6">
+      <c r="F10">
         <v>0.246</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>98.09999999999999</v>
       </c>
-      <c r="L6">
+      <c r="L10">
         <v>0.240972733971997</v>
       </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>-0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
         <v>2590.9</v>
       </c>
-      <c r="V6">
+      <c r="V10">
         <v>3.886738673867387</v>
       </c>
-      <c r="W6">
+      <c r="W10">
         <v>0.02763380281690141</v>
       </c>
-      <c r="X6">
-        <v>0.3365292980059316</v>
-      </c>
-      <c r="Y6">
-        <v>-0.3088954951890301</v>
-      </c>
-      <c r="Z6">
+      <c r="X10">
+        <v>0.33634238491621</v>
+      </c>
+      <c r="Y10">
+        <v>-0.3087085820993086</v>
+      </c>
+      <c r="Z10">
         <v>0.01364317288390066</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.04930214755172631</v>
-      </c>
-      <c r="AC6">
-        <v>-0.04930214755172631</v>
-      </c>
-      <c r="AD6">
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.04929742688757001</v>
+      </c>
+      <c r="AC10">
+        <v>-0.04929742688757001</v>
+      </c>
+      <c r="AD10">
         <v>25727.2</v>
       </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
         <v>25727.2</v>
       </c>
-      <c r="AG6">
+      <c r="AG10">
         <v>23136.3</v>
       </c>
-      <c r="AH6">
+      <c r="AH10">
         <v>0.9747440686827967</v>
       </c>
-      <c r="AI6">
+      <c r="AI10">
         <v>0.8711428348914931</v>
       </c>
-      <c r="AJ6">
+      <c r="AJ10">
         <v>0.971995009011507</v>
       </c>
-      <c r="AK6">
+      <c r="AK10">
         <v>0.8587510856735631</v>
       </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fast Finance24 Holding AG (XTRA:FF24)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0.008</v>
+      </c>
+      <c r="V11">
+        <v>0.002846975088967972</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0.05649599878605081</v>
+      </c>
+      <c r="Y11">
+        <v>-0.05649599878605081</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.05599706287084563</v>
+      </c>
+      <c r="AC11">
+        <v>-0.05599706287084563</v>
+      </c>
+      <c r="AD11">
+        <v>0.126</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0.126</v>
+      </c>
+      <c r="AG11">
+        <v>0.118</v>
+      </c>
+      <c r="AH11">
+        <v>0.04291553133514987</v>
+      </c>
+      <c r="AI11">
+        <v>0.001672729203727796</v>
+      </c>
+      <c r="AJ11">
+        <v>0.04030054644808743</v>
+      </c>
+      <c r="AK11">
+        <v>0.001566690565336307</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hypoport SE (XTRA:HYQ)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.057</v>
+      </c>
+      <c r="E12">
+        <v>0.04480000000000001</v>
+      </c>
+      <c r="F12">
+        <v>0.415</v>
+      </c>
+      <c r="G12">
+        <v>0.07451973823094785</v>
+      </c>
+      <c r="H12">
+        <v>-0.02681021743719654</v>
+      </c>
+      <c r="I12">
+        <v>-0.0034621068186616</v>
+      </c>
+      <c r="J12">
+        <v>-0.0034621068186616</v>
+      </c>
+      <c r="K12">
+        <v>34</v>
+      </c>
+      <c r="L12">
+        <v>0.07177538526493561</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>-0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>65.7</v>
+      </c>
+      <c r="V12">
+        <v>0.05644329896907217</v>
+      </c>
+      <c r="W12">
+        <v>0.1011302795954789</v>
+      </c>
+      <c r="X12">
+        <v>0.05736541373323574</v>
+      </c>
+      <c r="Y12">
+        <v>0.04376486586224315</v>
+      </c>
+      <c r="Z12">
+        <v>2.376818866031108</v>
+      </c>
+      <c r="AA12">
+        <v>-0.008228800802809832</v>
+      </c>
+      <c r="AB12">
+        <v>0.05497600884146238</v>
+      </c>
+      <c r="AC12">
+        <v>-0.06320480964427221</v>
+      </c>
+      <c r="AD12">
+        <v>191.6</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>191.6</v>
+      </c>
+      <c r="AG12">
+        <v>125.9</v>
+      </c>
+      <c r="AH12">
+        <v>0.1413396282089112</v>
+      </c>
+      <c r="AI12">
+        <v>0.3305157840262204</v>
+      </c>
+      <c r="AJ12">
+        <v>0.09760446546243894</v>
+      </c>
+      <c r="AK12">
+        <v>0.2449416342412451</v>
+      </c>
+      <c r="AL12">
+        <v>4.55</v>
+      </c>
+      <c r="AM12">
+        <v>1.92</v>
+      </c>
+      <c r="AN12">
+        <v>122.8205128205128</v>
+      </c>
+      <c r="AO12">
+        <v>-0.3604395604395604</v>
+      </c>
+      <c r="AP12">
+        <v>80.70512820512819</v>
+      </c>
+      <c r="AQ12">
+        <v>-0.8541666666666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EV Digital Invest AG (DB:ENGL)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>-0.9487750556792872</v>
+      </c>
+      <c r="H13">
+        <v>-0.9487750556792872</v>
+      </c>
+      <c r="I13">
+        <v>-1.183287934650496</v>
+      </c>
+      <c r="J13">
+        <v>-1.183287934650496</v>
+      </c>
+      <c r="K13">
+        <v>-4.89</v>
+      </c>
+      <c r="L13">
+        <v>-1.089086859688196</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>1.49</v>
+      </c>
+      <c r="V13">
+        <v>0.4613003095975232</v>
+      </c>
+      <c r="W13">
+        <v>-0.7287630402384501</v>
+      </c>
+      <c r="X13">
+        <v>0.07003924009790427</v>
+      </c>
+      <c r="Y13">
+        <v>-0.7988022803363544</v>
+      </c>
+      <c r="Z13">
+        <v>0.4804803965217938</v>
+      </c>
+      <c r="AA13">
+        <v>-0.5685466560403245</v>
+      </c>
+      <c r="AB13">
+        <v>0.05062305015347868</v>
+      </c>
+      <c r="AC13">
+        <v>-0.6191697061938032</v>
+      </c>
+      <c r="AD13">
+        <v>0.536</v>
+      </c>
+      <c r="AE13">
+        <v>5.634814132903634</v>
+      </c>
+      <c r="AF13">
+        <v>6.170814132903635</v>
+      </c>
+      <c r="AG13">
+        <v>4.680814132903635</v>
+      </c>
+      <c r="AH13">
+        <v>0.6564127367761978</v>
+      </c>
+      <c r="AI13">
+        <v>0.7092226128090282</v>
+      </c>
+      <c r="AJ13">
+        <v>0.5916981557479166</v>
+      </c>
+      <c r="AK13">
+        <v>0.6491380926800806</v>
+      </c>
+      <c r="AL13">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AM13">
+        <v>-0.139</v>
+      </c>
+      <c r="AN13">
+        <v>-0.128352490421456</v>
+      </c>
+      <c r="AO13">
+        <v>-558.8888888888889</v>
+      </c>
+      <c r="AP13">
+        <v>-1.120884610369645</v>
+      </c>
+      <c r="AQ13">
+        <v>36.18705035971224</v>
       </c>
     </row>
   </sheetData>
